--- a/data/RBP_validated_final.xlsx
+++ b/data/RBP_validated_final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\catia\Desktop\Blackboard\2_semestre\PB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\home\dr3cas\RBPScore\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92FD66BE-3002-4179-AC77-4E616D3CF9FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40EDC59B-5706-4388-9CD5-36A7BF559919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{9E04481C-FC71-490C-A348-3B01FD97F5C7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9E04481C-FC71-490C-A348-3B01FD97F5C7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,8 +28,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="706">
   <si>
     <t>Gamaleyavirus</t>
   </si>
@@ -16307,9 +16305,6 @@
     <t>Phage Delineation (pb)</t>
   </si>
   <si>
-    <t>NC_000929</t>
-  </si>
-  <si>
     <t>pdb_00005yvq</t>
   </si>
   <si>
@@ -23605,6 +23600,476 @@
   <si>
     <t>FASTA</t>
   </si>
+  <si>
+    <t>&gt;NC_000929 Enterobacteria phage Mu, complete genome
+TGTATTGATTCACTTGAAGTACGAAAAAAACCGGGAGGACATTGGATTATTCGGGATCTGATGGGATTAG
+ATTTGGTGGGGCTTGCAAGCCTGTAGTGCAAATTTTAGTCGTTAATCAATGAAACGCGAAAGATAGTAAA
+AAATTGCTTTTGTTTCATTGAAAATACGAAAAACAAAAACACTGCAAATCATTTCAATAACAGCTTCAAA
+AAACGTTCAAAACCGATAACAACCAAGCTGTCACCAAATGACTCATATCACAAATCAGCTTATGCCGTTT
+AGGTATGTTACATGTGTGATTATGTGAGGTGAAGTATGTTTTAGCTGGTTCATGGTTGTTATACGGCTTT
+TTTTACCTCCTGTGGTTCCTGTGAAGGTACTACAACACTTTCCTGTTCATGAATCCCATACTTTGACAAA
+ATCTCTTTGCGTTTTTCTTCAGGTAATGCATCTAGCATCATCAACGTCTGAATACTTTGCTGTGAAAATC
+CTATAAAGCTGTAAAGTTTCTGTTCATTAAATACAAGAGGCATTAACGCCAACAACCCCCCTTTACTTAA
+AAGTTTCAGTGCCTTGCGTGCTTCATCTGGTTCCAGCTCTTCAATCATATTGATTAAGGTTGTGGTTAAT
+TTGTTTATCAGTTCCGAAGAATCCTGTTTCTCATTGGCTTGAGCACCAGTATCCGGTGTGGATAACCCCA
+AGTGCGCAATAACTTGCTCTCGTTCTTTGGTGGGCATCGACATCACATCGTATTCAACAGCTTTCCCCCC
+CTTGACACCTTCCTTTTTTTGCTTCGTCCAGCCTTGAACATTTGCTCGATAGTGAACACCAGCAACAGAT
+CCAGGCATACCATCAGCAGCCATAATTTCTTGCGGCGAACACCAAATTGACTTTTCAGTATTATTCTTTT
+CTATAAAGTTACTTTTCAAAATTTAAACTCCTTATTTATCAACGCGTTAATCAGTAATCAAAGGAATTTA
+CCAAAAAGCAGCTTTACAAAAAGCTTTTCAGTAATTATCTTTTTAGTAAGCTAGCTAAGTTTTTACACTT
+AGTTAAATTGCTAACTTTATAGATTACAAAACTTAGGAGGGTTTTTAAATGTGTTCCAACGAAAAGGCCC
+GTGATTGGCATCGTGCGGATGTGATTGCGGGACTTAAGAAAAGAAAGCTCTCTTTATCAGCTCTTTCCCG
+GCAGTTTGGTTATGCGCCAACTACATTAGCTAATGCGCTAGAACGACACTGGCCAAAGGGTGAGCAGATT
+ATTGCTAACGCCTTAGAAACTAAACCGGAAGTAATCTGGCCTAGCCGATATCAAGCAGGTGAATAACATG
+GAACTTTGGGTATCACCGAAAGAGTGTGCGAATCTTCCTGGTTTGCCGAAAACATCGGCTGGTGTGATTT
+ATGTTGCTAAAAAGCAAGGATGGCAAAACCGCACTAGAGCAGGTGTCAAAGGTGGTAAAGCAATTGAATA
+CAATGCGAACTCTTTACCTGTTGAAGCGAAAGCGGCGTTATTGCTGAGACAAGGAGAGATTGAAACAAGC
+CTGGGGTATTTTGAAATCGCCCGCCCCACGCTGGAAGCCCATGATTATGATCGTGAGGCACTGTGGAGCA
+AATGGGATAACGCCAGCGATTCCCAGCGCAGACTTGCTGAAAAATGGTTGCCTGCGGTTCAGGCTGCAGA
+CGAAATGCTGAACCAGGGGATTTCAACGAAAACGGCTTTTGCGACCGTTGCAGGGCATTACCAGGTCAGC
+GCATCCACTTTGCGGGACAAGTATTACCAGGTACAGAAGTTTGCGAAGCCTGACTGGGCGGCTGCACTTG
+TTGATGGACGTGGAGCATCCCGTCGCAATGTTCACAAAAGTGAATTTGACGAGGATGCCTGGCAGTTTCT
+GATTGCAGATTATCTGCGACCGGAAAAACCCGCTTTCCGCAAATGTTATGAGCGTCTGGAACTGGCAGCC
+CGCGAGCATGGCTGGAGTATTCCCTCCCGTGCCACGGCCTTTCGCCGGATTCAGCAACTGGACGAGGCAA
+TGGTTGTTGCCTGTCGTGAAGGTGAACATGCACTGATGCATCTGATACCGGCACAGCAGCGAACTGTGGA
+ACACCTGGACGCCATGCAGTGGATCAACGGCGACGGTTATCTGCATAACGTCTTTGTACGCTGGTTTAAC
+GGTGATGTGATCCGTCCGAAAACATGGTTCTGGCAGGATGTGAAAACCCGAAAAATTCTGGGCTGGCGCT
+GCGATGTGAGCGAGAACATTGATTCAATTCGCCTCTCGTTCATGGATGTTGTGACTCGCTACGGTATCCC
+GGAGGATTTTCACATCACCATTGATAACACCCGTGGTGCTGCGAATAAATGGCTGACGGGAGGCGCGCCC
+AATCGCTACCGCTTTAAGGTAAAAGAGGACGATCCAAAAGGACTGTTTTTACTGATGGGGGCGAAAATGC
+ACTGGACAAGCGTTGTTGCCGGTAAAGGCTGGGGCCAGGCAAAACCTGTTGAACGTGCTTTCGGTGTTGG
+TGGGCTTGAGGAATACGTTGATAAGCATCCGGCACTGGCTGGCGCATATACGGGGCCAAATCCGCAGGCA
+AAACCTGATAACTATGGCGACCGCGCTGTTGATGCAGAGCTGTTTCTGAAAACCCTTGCCGAAGGTGTGG
+CGATGTTCAATGCCAGAACAGGCCGTGAAACAGAAATGTGCGGGGGCAAACTCTCGTTTGATGATGTTTT
+CGAGCGTGAATACGCCAGAACGATTGTGCGTAAGCCAACCGAAGAACAAAAACGGATGCTGTTACTGCCT
+GCCGAGGCGGTGAACGTTTCACGCAAAGGCGAGTTTACGCTTAAAGTTGGCGGCTCCCTTAAAGGCGCGA
+AAAACGTTTATTACAACATGGCATTAATGAATGCCGGCGTGAAAAAAGTTGTGGTCAGGTTTGATCCGCA
+GCAGCTACACAGCACGGTTTATTGCTACACCCTGGACGGTCGGTTTATCTGTGAAGCGGAATGTCTGGCA
+CCTGTTGCATTTAATGATGCTGCGGCAGGCCGTGAATATCGCCGCCGCCAGAAACAACTGAAATCTGCGA
+CGAAAGCAGCCATTAAGGCGCAGAAACAAATGGACGCGCTGGAAGTTGCTGAACTGCTGCCGCAGATAGC
+CGAACCAGCAGCACCAGAATCACGAATTGTTGGTATTTTCCGGCCTTCCGGTAATACGGAACGGGTGAAG
+AATCAGGAGCGTGATGATGAATACGAAACTGAGCGTGATGAATATCTGAATCATTCGCTGGATATTCTGG
+AACAGAACAGACGTAAAAAAGCCATTTAATTAACGTTTAAACAAAATTTAATTACGAGGTTATTCAGATG
+AATATTTCCGATATTCGCGCAGGACTGCGCACGCTTGTAGAAAATGAAGAAACCACCTTTAAACAAATTG
+CTCTTGAGAGCGGGCTTTCTACCGGAACTATCAGTAGTTTTATCAATGATAAGTACAACGGGGATAACGA
+GCGTGTTTCACAAATGCTGCAACGCTGGCTGGAAAAATATCATGCAGTGGCAGAACTACCTGAACCGCCC
+CGCTTTGTGGAAACGCAGACGGTAAAACAAATCTGGACAAGTATGCGTTTTGCCAGCCTGACTGAAAGTA
+TTGCTGTTGTATGTGGCAATCCTGGTGTGGGCAAAACCGAAGCGGCCCGTGAATATCGCCGCACCAATAA
+CAATGTCTGGATGATCACCATTACGCCATCCTGTGCCAGCGTTCTGGAATGTCTTACTGAACTGGCGTTT
+GAGCTGGGAATGAATGACGCACCACGCCGTAAAGGGCCGCTCTCCCGCGCCCTGCGACGTCGCCTTGAAG
+GTACACAGGGGCTGGTTATCATCGACGAAGCTGATCATCTTGGTGCCGAAGTTCTGGAAGAACTCCGCCT
+GTTACAGGAATCAACCCGTATTGGCCTTGTGCTGATGGGAAATCACCGGGTTTATTCAAATATGACGGGG
+GGTAACAGAACGGTTGAATTTGCCCGTCTGTTTTCCCGTATTGCAAAGCGCACTGCAATTAATAAAACCA
+AAAAAGCCGATGTAAAAGCTATTGCGGATGCCTGGCAGATTAACGGCGAAAAAGAACTGGAGTTATTACA
+GCAGATTGCGCAGAAACCAGGTGCGCTTCGCATTCTGAATCATTCACTTCGCCTTGCAGCCATGACGGCT
+CACGGTAAAGGTGAGCGTGTTAACGAAGATTATCTGCGTCAGGCTTTCCGTGAATTAGACCTGGACGTTG
+ATATTTCAACGCTGCTGCGTAATTAAGAAGGAGAAGAAATTATGATGGCCCGAAATATAAAAATGGCAAC
+GGATGCGCAGAACTGGTTACAGGCGCGCGGGAGTCATGTAAATGAATCATATCTCGGCGTGGCGCGTCCG
+ATTCTTGAAATCACTTACCCACCGGTGGAACTGGTAAAAAACGCGGTCAGAATTATGGAGCATAAGTCCG
+GGGTGGCCCGTTCTGTATGGACGGCCCGTCTTAATGGTTGCCAGATTATCTGGAGATAACGATGTGTATT
+AAAGCTGAAAAATATATTGAATGGGTTAAACACTGTCAGTGCCACGGGGTGCCGCTGACGACATATAAAT
+GCCCCGGATGTGGTGAACAGATTATGACGCAATGCTCACCCGAAAAGGAAATTCGGGATTCCCTGACATG
+TTGTCCGTGGTGCAGCGCAGTTTTCTTTAAACAGGTAAAAGGCGCGAAGGTAAAAGCCAGCGCGGTTATT
+CAGAATCAATAAGGTGAAACAAAATGGCAAAAGTAATTATTGAAATTAAAAATACAGTATCTGGAATTAA
+AGGACGGAATTTGCGCACCAGCATTGCGGTGGACGGTAGTGCGGAACTGGACGGTGATGAGGGTACACTT
+GCTGGCATGGTGGCGTTACTGGTGCTTAATAAAAGCCAGAAAATAATTAATGAGTCAGCCCATGAAGCTA
+TTGAGATTTTGAAAAACGATGGTGTCATCACCAGTGGTCGTGTCACTGAAATGGCTGTTGAAAAAACATG
+TCACTGAAAGGAACGCTGACAATGAATGTCAAAATCCGAAATGAAATTCAGGCATTAATCCGAATTCAGG
+AACGCAATAACAACGGTGGTGAATTACGCGAGTTTATTTGTGCGCGTGAAGTTGATGGCTATGGTGAAAA
+AACTTACCTGATTACTTTCGACCATTACAGCATCTGTGCGCGTTATTGCGGCGAAAGCATATCCCGCGCC
+ATTGCGTCTGGCGATGCGTTTAACGTGGATTTATGGGAGTACGTCATGGACCGGGAATACATCTGCGCAT
+CAGACCCTGAAGCCCGTGAAATGTGGCAGCGTATCTGGCGCGATTACCGGTTAATGGCAAAAGGCTGGGC
+GCGCTGCTGTTATTCCTCGCTTGCCCTGAAAGCGGTTCAGTTATCGCTGCGGCATATTCCGGCATCACTG
+CGCGAGCCTCTGCTGTACTGAATGGTGACTGACATGAAGTGTAATCGTAAGCGCTGGTCACGCGAAGACC
+GGGAATTTATCGAAGCCAACGTCGGGAAAATGACCGTTGAAGAAATGGCGGAAAAACTGAAAGTCGCCAC
+AACCGCCCTCCGGGCACATGCCAGAAGGCACGGAATATCATTGTGTGTATACCGAATCAGTGAACACGAC
+AAATATTTATGTCGTGAACTTTATAAAGAAGGACTGGATATTCATGTTATTGCCCGAAAGATGGAATTAA
+GCAATCGAGCTGTATCCAGCATTGTATACAGCGGATATTAATTAACAGGAGCTTTAATTTATGGCTAAAC
+CAGCAAAACGTATCAAGAGTGCCGCAGCGGCTTATGTGCCACAAAACCGCGATGCGGTGATTACCGATAT
+TAAACGCATCGGGGATTTACAGCGCGAAGCATCACGTCTGGAAACGGAAATGAATGATGCCATCGCGGAA
+ATTACGGAGAAATTTGCGGCCCGGATTGCACCGATTAAAACCGATATTGAAACCCTTTCAAAAGGCGTTC
+AGGGATGGTGTGAAGCGAACCGCGACGAACTGACGAACGGCGGCAAAGTGAAGACGGCGAATCTTGTCAC
+CGGTGATGTATCGTGGCGGGTCCGTCCACCATCAGTAAGTATTCGTGGTATGGATGCAGTGATGGAAACG
+CTGGAGCGTCTTGGCCTGCAACGCTTTATTCGCACGAAGCAGGAAATCAACAAGGAAGCGATTTTACTGG
+AACCGAAAGCGGTCGCAGGCGTTGCCGGAATTACAGTTAAATCAGGCATTGAGGATTTTTCTATTATTCC
+ATTTGAACAGGAAGCCGGTATTTAATACCACCATTAATATTTAATTAATTCACATTCTTTTAATTATGGC
+GCGATACGTCAGGAGATTGCTCGCGCCTGAAACAGATTACTGAGGAATAAAACATGGTTGATGCAAAAAT
+TCTGAATGGTGTCAGCACATTATTACGGGCTTACGGACGCCTGACCTGCGGAGTTCTGGCTGAAAAAATG
+AATATGCTGCCCTCGTCAATGGTGTATTTCCTGCGTGATGCGGTTGATGCCGGAGTGCTCACCGAATGCA
+ACGGATTTTATGACGTTCCGCGCCCGCGTCCGACGCCGCCTGTAAGACGAAACGCAACTGAGCAGCCTGC
+TGTTGATGATGCGGTGTGGTGCAACTGGCGTCGCTCATTACCCTGGGTGGAAGGTAATACCATCCCCGCG
+CTGGCAAAAGAGTTTGCGACGGGCGTGCTGACCTGTGAGTCAGTCCACATTGTTGCTGAGGTGGATAACA
+GAATGTGCGAACAGGGAATGCCCCGTTTTGTGATGGCTTATATCGATATCCGGCTGGGGCGTTTTATTTG
+CAGTTCAAGCGTCTGGAATATCACCGACCATGTACTGCGTTATCTCATTCTTGATTGTTCTCCGGCTCCC
+GCAGCGGTGCAGGAGGTGGCGTGATGTTTTTTAAAACGTCAAATCCCGCAGCACTGCTGGCGTGGGACCA
+GTTTATGGCGGACTGTCTGAAACTACGCGAAGAAGCCCGCCATCTTGATAAGGTTCTGGGTTGTGGTTGC
+CGGTCAGTATTCAGCACAAGTATTGGTGGGCGTTATTTTCATGGTGTGAACTTTCCGGGGAATGAGCGCC
+CTTTCTCGCGGGAGCTGTGGACCGTACAACGGCCCGCATCAGGTAACAGTTGCAGGCCCAGAACTTCGCG
+GATACCTGCTCATCTCAGGGAGCAGGCAAGAGAGCTGGCGAAAATATGGCAGGAGAATATTCCGGTCACT
+TACGCCCGCACAGACGCTCTTTTACCCGCACTGGGACTGGATTTCAGCGCAACAATATTCGGGCCGCTCC
+AGTGGTTCCGTGTTGGTGATGTGATTTACGTCATGACGGGGATGACACCCGCGCAAGGCCGCATGACTGA
+AATCCTTTCTGACGAATTTATCCGGGCGCAAAAACAGGCGGAGGTAAACAATGGAAAACAATAAAACATC
+GTATTCGTGGCTGGGGAAATTCACCACGGTGAAACAGGAATGCCCGACCTGCGGTAATGAATCCCCTGAA
+TATCTGAAAGAGTGCCCTCATTGTGGCGGGCTGAAATGCAACCACTGCGATATGGGCGATGACACAGCGT
+GCATGAATTGTGAAGGTGAATAATATGAATAATGAAACTAAATTTACTCCCCTTAATATTGATAACGTCA
+TGGCTGAAAAAGGGATGCTGGAACGTGTTCGCGCTATCGTTGAATATGGTATTAAGCATAATCTCACCGC
+CAGAGAAGTCCGTGACATTATCAACCGCGAAATGAATCGTCTGGAAACAGTAGTGGCACTGCAAAATGAA
+ACAGCCCGCGAGGAGTACATCCGCCGCAGGCTGGGGCTATCAGACCAGGATATTGTTACTGACGCTCATG
+TGTTTGAGGCTTTTGAGATCCGTCAGCATCTGGGTCTAACGAACTGATAATGTCTTCCATGATCTTTGAC
+AGTTGCAGTTTTTCGCGGCGGCTTGTTCTCATTGCAGGCGCATCTTTTAAAATCTCTGCTGAAGAGCTGA
+AAATGGCTTTGCCCTCTTCTGCGGTGATGATCGCCTTCTTCACCAGAAGGCGCACCAGTGCTGATGCAAT
+CGCATAACCTGCAACATCATAAGGTTGTACATTATTTTCCATAAAATCCTCTCTGATTGATGTGTAAATT
+CAGGCGGTGTTGCAGCACCGCCCCCTTTCCGGAGGTACGATCATGAGTCGCACATCCCTGATTAAATTAA
+TCCATGTCGCCCGTCGGGAGCTACAACTCGACGACGACACTTACCGCGCTTTTCTGATGCAGAAAACGGG
+CAAAATCAGTTGCCGCGAGCTGACGGTCACGCAACTGGAACAGGTGCTCGGTGCCATGAAAGAACGCGGC
+TTTAAGAAGCAGAATAAATACCCCCGTCGCCGCTTTAAGGGGCATGTCACGCCCCGTGAGAAGGTGTATA
+AAATCTGGCAGCAGATGGCAGAAGACGGTTTTATTACCGATGGCGGTGATGTGGCGCTGGATAAATATGT
+TCAGCGCCTGACCGCGAAACGCAACGGCGGACAGGGCGTTTCCACACTGGCGTGGTGTCATGGCGACACG
+CTGCTGACAGTCCTCGAAACACTCAAGCAGTGGCACATCCGCTGTATTCGTGAAGCCTTTTCCCGTCACG
+GGCTTCCATTGCCGGTCAGTCCGTCCGGTCGTGAACTGCGCGGCTATGATGCCATGACGGCGGCTTATGC
+CCATGCCAGAAAGACACGGAGGATGGCACAATGACGGAAGATTTATTTGGTGATTTGCAGGATGACACCA
+TCCTGGCACATCTTGACAATCCCGCCGAGGATACGTCACGCTTTCCGGCACTGCTGGCGGAGCTGAACGA
+TTTACTGCGCGGGGAATTGTCCCGGCTGGGTGTTGATCCTGCCCATTCACTGGAGATTGTTGTGGCTATC
+TGTAAGCATCTGGGCGGCGGTCAGGTCTACATTCCACGCGGTCAGGCTCTGGACTCGCTGATTCGGGATT
+TGCGTATCTGGAATGATTTTAACGGTCGCAACGTCAGCGAACTGACCACCCGTTATGGTGTCACTTTCAA
+TACGGTGTACAAAGCCATTCGCCGGATGCGACGGCTGAAATACCGCCAGTACCAGCCCTCACTTCTGTAA
+ACAGTAAAGCCGGTTAATCCGGCTTTTTTTACGTCCTCAATATCCTGTGATGAATAACCGTACCGGGGAA
+AATCATCATGGGTAAAGGCTGGAATGCATCCTTTCATCTTGGCAGACGTGAGCGGCTGCGTCAGGAGGTT
+TTGCACCGTGTCGCCGGTGGGCCACGTCCTGCGCCCCGCGACTATACCGGTCATGATGGCACCCACGGCA
+GTTATTACATGAAAGGCTGGCAGTCAGTTGATATGCCGGAAATTCTTCATCATTGCCTGCTTTACAGGGA
+GAAACATTATGTCTGAGCGTTCTGCTCGTCAGTGGCCTGATTTTTTATCGGTGGTGTTACTGGCGCTGTT
+ATTGTGGATAAGTCTGTTTTGTGGCTGGCGCGCGCTGATGTTTTGCTGTGCCTCGGTTTTCAGTGTTGCT
+TTATGTGTTGCCGCTGATTGTCTGGATGCGCTGATAATGAGCTGCCGGGTGCCTGAACATTTTGCCCGGT
+TCGTCTGGCCTCTGACCTGGCTGGGGAGTCTGTCCGGGCTGGGATTAGCCGTGATGGCAACGTCTCAACT
+GAAAACGGGTCCTGAGCATGTCATCTGGGCGCTGGCCGGATTGCTGACGTTCTGGCTCTCATTTCGTTTT
+CGCGCTCGTCTGTTCGGGTAAAGGGGCACCATGTACAGAAAATTCAGTGATGAATGTTTCGGGCCGTCCA
+CGCTGATTAATGCGATAAAAGTGATTGCCCTTGTGGTTCTGATAACCATCAGTGCCGTGGTGTATCTTTC
+TGTCTGTTAACCGGGGGAAAATATGCAGCATGATTTATTTGAACACGATCCGGCAATTCGCCAGTTAATC
+GGACATATTGATAACATCCCGGCCCCGGAACTGGAATCACGCTGGCCCCGTTCGGTGGTTGATCTGATTG
+ATGTTCTGGAAAACGAACTGAAACGCCAGAACGTCAGCAATCCCCGTGAACTTGCCCGTAAACAGGCCGT
+TGCCCTGTCCTGTTTTCTGGGTGGACGGCAGTTTTACATCCCCTGCGGCGATACGATCCTGACCGCGTTA
+CGCGACGATTTGCTTTACTGCCAGTTTAATGGTCGTAACATGGAAGAACTGCGTCGCCAGTACCGCCTGT
+CCCAGCCGCAGATCTACCAGATTATTGCCCGCCAGAGAAAGCTGCATACACGACGTCATCAGCCTGATCT
+GTTCTCACCTGAAACCCCAAAATAACCGGCATCCTGCCGGTTATTTCCTGTCACCATAATCCCGCACCTG
+CCACCTGATTTTTTAGACTGCCATCAGAGAATTTTTTCAGGGAAGCATGATGGCGGGGATACCAAAAAAA
+CTGAAAGCCGCACTGCTGGCTGTAACGATTGCCGGTGGCGGAGTGGGTGGTTATCAGGAAATGACCCGTC
+AGTCTCTGATCCACCTGGAAAATATCGCTTATATGCCTTACCGCGATATTGCCGGTGTGCTTACGGTCTG
+TGTGGGACATACCGGGCCGGATATCGAAATGCGCCGTTACAGCCATGCGGAGTGTATGGCTCTCCTCGAC
+AGTGATTTAAAACCGGTTTATGCGGCAATCGATCGTCTTGTCAGGGTGCCGCTGACGCCATATCAGAAAA
+CGGCGCTGGCAACGTTTATTTTCAACACCGGTGTTACCGCATTCAGTAAATCAACGCTGCTGAAAAAACT
+CAATGCCGGTGATTACGCCGGAGCGCGTGACCAGATGGCCCGCTGGGTGTTTGCCGCAGGCCATAAATGG
+AAAGGACTGATGAACCGTCGCGAAGTGGAAATGGCAATCTGGAATATCAGGGGGGCGGATGACCTTCGCC
+AGTAAAAGTTTACTACTGGCAGCCGTGTTTACCGCCGTTCTGTCCGGGGGGTTGTGGCACAGGCTGGACA
+GCACCCGCCACGATAACCAGACGCTGCGCCGTGAATTACAGACGGAGCAACAGGCCCGCCACACTGCTGA
+ATGGTTGTTACACGGTCAGGAACAGACGATGCAGGTATTTTCCGCTATCCGTGCCGCAAATCGTGCCGCA
+CGGCTGGCAGATGAGACAGAACATCATGATGCAAAAGAAAAAATTACAACCGCCATTACTGGTGACAATT
+GCAGCACTCGTCCTGTGCCTGCCGTTGCTGCTGACAGGTTGCGGGAACTCGAAAAACGCACCCGTGCCAT
+CGGTGGTGATCCTGCCCGAAATTGATACAGAACTGACGGAAGCAACGCCCGTTCCGCCCATGCCACAGCC
+CCTGACGTGGGGAGCATCCCTTCTCTGGAATGCTGACCTGTTGATGGCGCTCGGGCAGTGCAACCGCGAC
+AAGGCATCAGTCCGGGAACAGGAGATCCGAAGGAAAGAAATTTATGAACGAAGACCAGAACCGGGCGGTG
+GCGCTGCTGCTCGCTGAACTCTGGCAGGGGGATACCCGTGATATTCCCCGCCCGGCGGCGTATGACCCGC
+CTGTATTGTGTGCCGGTTGCGGTCGTGAGCTGCGGCCTGATGTGCTGAGACAGCAGCCGATGGCGAACTA
+CTGCCACTGGTGCCGTGGAGCAGAATAATGGATTTGATTTCAGTTTTAGCGTTATGGCCTTACCTGTTGC
+CTGTTGTGGCCGGTGGGGCCGTCTGGGCGATGCGTCGTAGTTTTGCCAGCACCGAGCGTGTGGAGCGTCT
+TGAAAACCGGATGACCGAAATGGAAACCCGCTACGCCAGCATCCCTGGCACAGAAGATGTACACGAAATG
+CGCCTGCGAATTGCAGAGCTGTCCGGCGATATCCGGGTGCTGTCCCAGCGGGTGCAGTCATTTTCCCATC
+AACTGGAGCTGCTGCTTGAAAACGCAGTAAACCGGAGTAATTCATGATTAACGATATTCTGACCGAAGAC
+CGTCGTCTGGTCATCCTGCGTTCCCTGATGGACTGCAATAACGAAGCAAACGAATCCATCCTTCAGGACT
+GTCTGGATGCATACGGACACAACGTTTCCCGCGATGTGGTTCGCGGCCAGATTGACTGGCTGGCAGAGCA
+GCAACTGGTCACCGTGGAAAACCTGCGCGGCTTTTATGTCGTAACGCTGACCTCCCGAGGTCAGGATGTG
+GCAGAAGGTCGTGCCCGCGTTGCCGGTGTCAAGCGTCCTCGTCCCCGTGCATGACAGGAGGCGTGATGGA
+CAGGAAAACACGGGGCCGGGCTTCAAAAGTGGATTTACTGCCGGAAAACGTACGTAAAACGCTGCATGAA
+ATGCTGCGTGATAAAGCGATCCCACAGGCCCGCATTCTGGAAGAAATTAACGCACTGATTGAAGACGCAG
+GCCTGCCGGATGAGATGAAACTCTCCCGTTCCGGTCTGAATCGTTACGCGACGAACGTCGAGCAGGTAGG
+CCATAACCTGCGACAGATGCGTGAAATGACGTCAGCACTGACCGCAGAACTTGGCGACAAGCCAATGGGA
+GAAACCACAAAGCTGATTCTGGAAATGGCCCGCAGCCAGCTTTTTAAGGCCATGATGCGGCAAATCGAAA
+ACCCGGAATCTGACGTGGATATTGACCTGCTGAAAAATGCCATGCTGGCGGCACAGCGTCTGGAATCCAC
+GGCAATGTCCAGCCACCGGCGCGAGAAAGAAATCCGCCAGGCATTCGCAGAAGAAGCGGCAAACGCCGTC
+AGTGAAGAACTGCGCGGGCAGGATGGCATCAGCGAAGAGCTGGAGCAGCGTATCCGTGATGTACTGCTGG
+GTAAGGCATGAGAGGGTTATGAACACCAGAGAAAACAACCTTAAAGCCCTTCATGCGCCCCGCAAAATCA
+ACCTGCGTGAGGAAGCCGGACTGCTCGGCGTGGATATCGTGACCGATATCGGGGAAGCACAGCCCCGCAA
+TGAACCGGTTTTTCTGGGCTATCAGCGCCGCTGGTTTGAGGATGAAAGCCAGATTTGTATTGCTGAAAAA
+TCCCGTCGTACTGGCCTGACGTGGGCCGAAGCAGGCCGCAATGTCATGACGGCAGCGAAGCCGAAGCGTC
+GCGGTGGTCGCAATGTCTTTTATGTGGGTTCCCGTCAGGAAATGGCGCTGGAATACATCGCCGCCTGTGC
+CCTGTTTGCCCGCGCCTTTAACCAGCTGGCAAAGGCTGATGTCTGGGAGCAGACCTTCTGGGACAGCGAT
+AAAAAAGAAGAAATCCTCACTTATATGATCCGCTTTCCGAACAGCGGATTTAAGATACAGGCGCTGTCAA
+GCCGCCCGTCTAACCTGCGTGGTTTGCAGGGGGACGTGGTGATTGATGAGGCGGCATTCCATGAAGCCCT
+GGACGAACTCCTGAAAGCGGCCTTTGCACTAAACATGTGGGGTGCCAGCGTGCGCATCATATCGACACAT
+AACGGCGTCGATAATTTGTTTAATCAGTACATTCAGGATGCGCGCGAGGGGCGCAAGGATTACAGCGTTC
+ACCGCATCACGCTGGATGATGCCATCGCTGACGGGTTATACCGACGTATCTGTTACGTCACGAATCAGCC
+GTGGTCGCCGGAAGCGGAAAAAGCCTGGCGTGATGGCCTGTACCGGAATGCGCCGAATAAAGAGAGTGCC
+GACGAGGAATACGGCTGCATTCCTAAAAAATCCGGGGGCGCTTATCTGTCACGCGTGCTGATTGAAGCCG
+CCATGACGCCAGCGCGGGATATCCCGGTTCTGCGTTTTGAAGCCCCGGACGATTTTGAATCGCTGACACC
+ACAAATGCGCCACGGCATCGTTCAGGACTGGTGTGAACAGGAGCTGCTCCCGTTGCTCGATGCGCTGTCG
+CCGCTCAATAAACACGTACTGGGCGAAGACTTTGCACGCCGTGGCGACCTGACGGTGTTTGTGCCGCTTG
+CCATCACGCCTGACTTACGCAAACGCGAATGTTTCCGCGTGGAGCTGCGTAATGTGACCTATGACCAGCA
+GCGACAAATCCTTTTATTCATTCTGTCCCGTTTGCCCCGTTTTACCGGCGCTGCATTTGATGCCACCGGT
+AACGGCGGTTATCTGGCAGAGGCCGCCCGTCTGATTTATGGCCCGGAGATGATCGACTGCATCAGTCTGA
+CCCCCGCCTGGTATCAGGAGTGGATGCCAAAACTGAAAGGCGAGTTTGAAGCGCAGAACATCACGATTGC
+CAGGCATCAGACCACACTTGATGACCTGCTTCATATCAAGGTGGATAAGGGGATCCCGCAGATTGACAAG
+GGGCGCACAAAAGATGAAGGCGGTAAAGGCCGACGACATGGCGACTTTGCCGTGGCGCTCTGTATGGCTG
+TCAGGGCGTCTTATATGAATGGTTTTGTTATCGACGAGGACAGCATACAGGCGCTGCCACCACGCCACCG
+TGGTGATGATGTTGATAACGATGATTTTGATGATTATCACCAGTTTGAACGAGGGGGCTGGTAATGGGCC
+GTATTCTGGATATTTCCGGGCAGCCGTTTGATTTTGACGATGAAATGCAGAGCCGCAGCGATGAGCTGGC
+AATGGTCATGAAGCGCACGCAGGAGCATCCTTCCAGTGGTGTGACGCCGAACCGGGCCGCGCAGATGCTG
+CGTGATGCCGAACGCGGTGATCTGACAGCACAGGCTGACCTGGCCTTTGATATGGAAGAAAAGGACACCC
+ACCTTTTTTCCGAACTGAGCAAACGCCGCCTTGCCATTCAGGCGCTGGAATGGCGCATCGCTCCGGCACG
+TGATGCCAGCGCACAGGAGAAAAAAGACGCCGACATGCTGAATGAATATCTGCATGATGCGGCGTGGTTT
+GAAGATGCCCTGTTTGATGCCGGTGATGCCATTCTCAAGGGCTATTCCATGCAGGAGATTGAATGGGGCT
+GGCTGGGGAAAATGCGCGTGCCGGTGGCGCTGCATCATCGCGATCCGGCGCTGTTCTGCGCGAACCCCGA
+CAATCTGAACGAATTACGCCTGCGTGATGCGTCTTATCACGGGCTGGAGCTGCAACCGTTCGGCTGGTTT
+ATGCACCGGGCCAAATCCCGCACCGGGTATGTCGGCACCAATGGCCTTGTGCGCACGCTTATCTGGCCTT
+TTATTTTTAAAAACTATTCCGTGCGTGATTTTGCAGAGTTTCTGGAAATTTACGGACTCCCCATGCGCGT
+CGGTAAATATCCGACCGGCTCAACGAACCGCGAGAAAGCCACGCTGATGCAGGCCGTGATGGATATCGGG
+CGACGTGCCGGTGGCATTATTCCGATGGGGATGACGCTGGATTTTCAGAGCGCCGCAGATGGTCAGTCAG
+ACCCTTTTATGGCGATGATTGGCTGGGCAGAAAAAGCGATTTCAAAAGCCATTCTGGGCGGCACCCTGAC
+CACAGAGGCTGGCGATAAAGGTGCGCGGTCGCTGGGTGAAGTGCATGATGAGGTTCGCCGGGAAATCCGT
+AACGCGGATGTGGGCCAGCTTGCCCGCAGTATTAACCGTGACCTGATTTATCCCCTGCTGGCACTGAACA
+GTGACAGCACCATTGATATTAACCGCCTGCCGGGCATTGTATTTGATACCAGTGAAGCGGGTGATATTAC
+GGCACTGTCTGACGCCATTCCGAAACTGGCGGCGGGAATGCGTATTCCGGTCTCCTGGATACAGGAAAAA
+CTTCATATTCCACAGCCGGTCGGTGATGAAGCCGTGTTTACTATACAACCGGTTGTCCCGGATAACGGTT
+CGCAGAAAGAGGCCGCATTATCCGCTGAAGATATCCCGCAGGAGGATGATATCGACCGGATGGGCGTCTC
+ACCGGAAGACTGGCAGCGTTCGGTTGACCCCCTGCTGAAACCCGTCATTTTTTCTGTGCTGAAAGATGGC
+CCGGAAGCCGCCATGAACAAAGCCGCTTCATTATATCCGCAGATGGATGATGCAGAACTTATCGACATGC
+TGACCCGTGCCATTTTTGTTGCCGATATATGGGGGCGTCTGGATGCCGCAGCAGACCATTGATCTGGCGT
+ATGCCGCGCGCCTCCCGCCAAAGGAGGCTGTCGCGTATTTCCGCGCCAAAGGCTACAACATCACCTGGAA
+CTGGTACGAACAACTGGCAGACGCGCACGCCCGCGCCTTTACCGTTGCCAAAGCCACCCGGATGGATGTC
+CTGACCACAATCCGTGAGGAAGTGGAGCGGGCTGTCAGTGAAGGCATCACCCGTGAGGAATTTACCCGCA
+CACTGGCCCCCCGGCTGCAAAAACTCGGATGGTGGGGAAAACAAATCATCGTGGATGCAGAGGGAAACGC
+GAAGGAAATCGAACTGGGCAGTCCGCGTCGTCTGGCAACCATTTATAACGTCAATACCCGTACGGCGTAT
+GGGGCAGGACGTTATGCGCAGATGATGAATACCGCCGATTTGTACCCGTACTGGCAGTACGTTGCCGTTA
+TGGATGGCAGAACACGCCCGGAACATGCGCGGCTGCACAATATGGTTTTCCAGTATGACGACATTTTCTG
+GCAGACGCATTACCCGCCCAATGGCTGGAACTGCCGCTGTCGCGTCCGGGCGCTGTCTGCGGCCCGCATG
+AAAGAACTGGGGCTACAGGTCAGTTATGGTGCGTCATTCATGAATACCCGCGAAGTGGATGCCGGTACGG
+ATGAAAGCACCGGAGAGATTTTCCGCACATCGTCAACCACGTTTGACAACGGTCGGGTAAAAATGACGCC
+AGATGTGGGCTGGTCATATAACCCCGGTTCGGCGGCATTTGGTACGGATCAGGCACTGATTCGAAAACTG
+GTGGAAGTTCGTGACGCGCAGCTGCGTGAGCAGGTTGTTCAGACGCTGAATAACAGCCGGGAGCGTCAGC
+TTGCTTTTTCCCTCTGGCTTAAACGCCTGGCAGGATCACGTCAGACCGGTCATGAAATCCGGGCGCTGGG
+GTTTATGACGGGATCCGTGGCTGAAGCCGTATATCAGCGCACCGGGAATATGCCAGCCCGTCTGCTTGTA
+ATGAACGGGAAAAGTCTGGCGACCACTGCTGATGCCGCCCTGAAACCGGAGGATTTACAGCGTCTGCCGT
+CGCTGATGGCAAAACCACAGGCGGTATTGTGGGACAGGGAGAACCACCAGTTGCTGTATGTTGTGGCAAC
+CCGTGACGGCACGGCCCGGATTGTGGTCAGAACATCACAGACAGTCGGCAGGCAGAATGACCGGGCGGAT
+GTGCTGGTCAGTATCAGCCGCGTATCTGCACAGTCGCTTGAAGCCGCGATTGCTGACGGGATGATTGACG
+TACTGGAGGGGCATGTGGAGGTGAATAAGTGAGTCTTGATATGAACGTTGCCGTGGATGTGCGACGTATT
+CAGCTTGCGCTGGATGAACTGGGAACCGTCACACGTGACCGCGCCATTCCCCGAGTGATGGCTGCGGCGC
+TGCTGTCATCCACGGAACAGGCATTTGAACGGCAGGCAGACCCGGATACAGGGAAAGGCTGGGAAGCGTG
+GAGCGATTCGTGGCTGGCATGGCGTCAGGATCATGGTTTTGTTCCGGGCAGTATCCTTACCCTGCATGGC
+GATCTGGCACGCAGTATTACCACCGATTATGGACAGGATTATGCCCTGATTGGTTCGCCAAAAATTTATG
+CTGCCATTCATCAGTGGGGCGGTACACCCGATATGGCACCCCGCCCGGCAGGCGTTCCTGCGCGTCCTTA
+TATGGGGCTGGATAAGACCGGGGAACAGGAAATTTTTGATGCCATCAGAAAACGCGTCAGCGCCGCTCTG
+AGGCAATAAACAGAATCAGGCATAAAATCAGCCGCACAGATTTTTTAAAACGCGCCACGGGATTTTTAAA
+CCGGTATTTAACGGTGTATGAATCCCGTTTTATCTTCCTTTCACTTTCTTTCTCCAGTACTCAAATAGCA
+TAACCCCAGATTTTCCCGCACCTCCCGCAAACTGACTGCTCACAAACCATGATGAGCAGCAGGACATGAA
+AAAACACGCGATTGGCATTGCCGCACTGAATGCGCTGTCCATTGACGATGACGGCTGGTGCCAGCTATTG
+CCTGCCGGTCATTTCAGTGCCCGTGATGGTCGTCCGTTTGATGTGACAGGCGGTCAGGGGTGGTTCATCG
+ACGGTGAGATTGCCGGGCGTCTGGTTGAAGGCGTTCGCGCGCTCAACCAGGACGTGCTGATTGATTACGA
+GCATAACCAGCTACGTAAGGACAAAGGATTACCCCCGGAACAACTCGTCGCGGCTGGCTGGTTTAACGCC
+GATGAAATGCAGTGGCGTGAAGGTGAAGGGTTATTTATCCACCCACGCTGGACGGCGGCGGCCCAGCAGC
+GCATCGATGACGGCGAATTTGGTTATCTCTCTGCGGTTTTTCCGTATGACACCGCCACCGGTGCGGTGCT
+GCAAATCCGCCTTGCTGCGCTGACCAATGACCCCGGTGCCACCGGCATGAAAAAGCTGACCGCACTGGCG
+GCAGACCTTCCCGACATCCTTCAACAGGAGAACAAACCCATGAATGAAACGCTGCGCAAGCTGCTTGCGC
+GTCTTGGGGTGACGGTCCCCGAAAATGCAGACATCACCGATGAACAGGCAACAGCGGCACTGACCGCGCT
+GGACACGCTGGAAATTAATGCCGGGAAAGTGGCGGCGTTGTCTGCCGAACTGGAAAAGGCACAGAAAGCC
+GCCGTTGACCTGACGAAATACGTCCCGGTGGAAAGCTACAACGCCCTGCGTGATGAACTGGCACAGGCGA
+CTGCACAAAGCGCCACAGCCAGCCTGAGCGCCGTTCTGGACAAGGCGGAACAGGAAGGCCGCATTTTCAA
+AAGCGAACGCACTTACCTGGAACAGCTTGGCGGTCAGATTGGCGTGGCGGCACTGTCGGCACAGCTTGAG
+AAAAAACAGCCCATCGCTGCGTTATCTGCCATGCAGACCACCACAGCGAAAATTCCGTCGCAGGAAAAAA
+CGGCGGTGGCGGTGCTGTCTGCTGATGAACAGGCAGCAGTGAAGGCGCTCGGCATTACAGAGGCTGAGTA
+TCTGAAAATGAAACAGGAACAAGAAAAATGATTGTCACCCCGGCATCCATTAAAGCCCTGATGACCTCCT
+GGCGTAAGGATTTTCAGGGCGGTCTTGAAGACGCCCCGTCGCAGTACAACAAAATTGCAATGGTGGTGAA
+CTCTTCCACCCGCAGTAATACGTATGGCTGGCTGGGTAAATTCCCGACCCTGAAAGAATGGGTGGGTAAG
+CGAACCATTCAGCAAATGGAAGCGCATGGCTACTCCATCGCCAATAAAACGTTTGAAGGCACCGTGGGTA
+TTTCCCGTGATGACTTCGAGGATGACAATCTGGGTATTTATGCGCCGATTTTTCAGGAGATGGGCCGTTC
+TGCGGCAGTTCAGCCGGATGAGCTGATTTTTAAACTTCTGAAAGATGGCTTTACCCAGCCCTGCTATGAC
+GGTCAGAACTTCTTCGACAAGGAGCATCCGGTATATCCGAATGTGGATGGCACGGGCAGCGCGGTTAATA
+CCTCCAACATCGTTGAGCAGGACAGCTTCAGCGGTCTGCCATTCTATCTGCTGGACTGCTCCCGCGCAGT
+CAAACCGCTGATTTTCCAGGAGCGCCGCAAACCGGAACTGGTCGCACGTACCCGTATCGATGACGACCAC
+GTTTTTATGGATAACGAGTTCCTGTTTGGTGCCAGCACCCGCCGTGCTGCCGGTTACGGCTTCTGGCAGA
+TGGCTGTCGCGGTAAAAGGCGATCTGACGCTGGATAACCTCTGGAAGGGCTGGCAACTGATGCGCTCTTT
+TGAAGGTGATGGCGGTAAGAAACTGGGCCTGAAGCCGACGCATATCGTTGTACCGGTCGGGCTGGAAAAA
+GCCGCAGAGCAACTGCTTAACCGTGAACTGTTCGCGGATGGCAATACCACCGTCTCCAACGAGATGAAGG
+GCAAGCTGCAACTGGTTGTCGCTGACTACCTGTAACCGTCATTAAAAGGCGGTTCAGACCGCCTTTTAAC
+CTGATTTAAAGGAAAAGGAGGAGCATGTGTTATGTCAGGCACTTCGCTTAATTCACAACGGCTGGACACT
+TCTCGCATCACTTGCACGGCGATTATTAAATGCCTTCGTCCGGTCTACCGCCGCGCCGGAATCGCCTTTA
+CGCGTGGCGAAAACACCGTGGAAGTCACCGAAGAACAACTGGCGATCATTCGTGCCGACAGCGTGCTGTC
+TGTGGTATCTGCATCGTCAGCAGAAACGCTCGCTGAGGCTGGGGGGCTGGACGTTCTGGGTGTGGGCGAT
+CTGAATACCCGTATCCGTGCGACCGTTGCCGGTCTGGATAAGGCAAACCCGGAGCACTTTACCGCAGGGG
+GAGAACCCAAAGTGAAAGCCGTCAGTGCGGCGCTGGGGGAACCGGTGAGCAGTGCGCAAATCAAAGCGGC
+GCTGGCTGAGGCGGATGCATGAATTACGCGACGGTAAATGACCTGTGCGCCCGCTATACACGTACGCGGC
+TGGATATTCTCACCCGCCCTAAAACAGCGGACGGGCAGCCGGATGATGCCGTGGCAGAACAGGCACTGGC
+AGATGCTTCGGCCTTTATTGATGGCTATCTCGCCGCGCGCTTTGTTCTGCCGCTTACCGTCGTCCCCTCA
+CTGCTGAAACGGCAGTGTTGCGTGGTGGCCTGGTTTTATCTGAATGAATCACAACCCACCGAGCAGATCA
+CCGCAACTTACAGGGACACGGTGCGCTGGCTGGAACAGGTGCGCGATGGCAAAACAGATCCCGGCGTGGA
+AAGCAGAACGGCAGCGTCGCCGGAGGGAGAGGATCTTGTGCAGGTTCAGTCTGATCCGCCTGTTTTTTCA
+CGAAAACAGAAGGGGTTTATCTGATGCTGGAAGAAACCGAAGCCGCACTGCTGGCGCGCGTTCGTGAGTT
+GTTTGGGGCAACCCTGCGGCAGGTGGAACCCCTTACCGGCACATGGACTAATGAGGATGTGCACCGTCTC
+TTTCTGGCCCCGCCATCGGTATTTCTGGCATGGATGGGCTGTGGTGAGGGGCGTACGCGTCGGGAAGTTG
+AAAGTCGCTGGGCATTTTTTGTCGTGGCGGAGTTGCTGAACGGGGAACCGGTAAACCGGCCCGGTATTTA
+TCAGATTGTGGAGCGACTGATTGCCGGTGTTAACGGTCAGACGTTTGGCCCGACCACCGGGATGAGGCTG
+ACGCAGGTCAGAAATCTTTGTGACGACAACCGTATCAATGCCGGTGTGGTGCTTTACGGCGTTCTGTTCA
+GTGGCACAACCCCGCTGCCGTCCGTAGTGGACCTGGATTCGCTGGATGATTACGAGCGTCACTGGCAGAC
+CTGGAAATTCCCGGACGAAACCCCGGAATTTGCCGCACATATCAATGTGAATCAGGAAAAGGATCATGAT
+GCTGAAAATTAAACCCGCAGCGGGAAAAGCCATCCGTGACCCGCTCACGATGAAATTACTGGCGTCTGAG
+GGAGAAGAAAAGCCCCGTAACAGTTTCTGGATACGTCGCCTTGCAGCCGGTGATGTGGTTGAAGTCGGGA
+GCACCGAAAACACGGCGGATGATACCGACGCTGCGCCGAAAAAACGGAGTAAATCGAAATGAGCGATATT
+TCATTTAACGCGATCCCGTCAGATGTTCGCGTTCCTCTGACGTATATCGAATTTGATAACAGCAATGCCG
+TCAGCGGAACACCGGCTCCCCGTCAGCGCGTGCTGATGTTCGGGCAAAGCGGAAGTAAAGCCAGTGCGGC
+ACCAAACGTGCCTGTCCGTATCCGTTCCGGCTCACAGGCCAGTGCGGCGTTTGGTCAGGGTTCCATGCTG
+GCACTGATGGCAGATGCATTCCTGAACGCTAACCGCGTGGCGGAGCTGTGGTGTATTCCGCAGGGGAACG
+GCACCGGTAATGCTGCTGTCGGTGAAATTTCACTGTCAGGAACGGCAGGCGAAAACGGCTCGCTTGTGAC
+TTACATTGCCGGTCAGCGACTGGCGGTATCTGTCGCAGCAGGTGCAACGGGAGCGGCGCTGGCTGACCTG
+CTGGTTGCCCGAATCAAAGGCCAGCCTGATTTACCGGTGACGGCAGAAGTTCGCGCAGACAGCGGGGATG
+ATGACACCCATGCAGATGTGGTTCTGAGTGCAAAATTTACGGGTGCATTATCTGCCGTGGACGTGCGCTG
+GAACTATTACGCGGGTGAAACGACCCCTTACGGGATTATCACGGCATTCAAAGCCGCCTCCGGGAAAAAT
+GGCAACCCGGATATCAGCGCAAGTATCGCGGGAATGGGCGATCTGCAATATAAATATATTGTGATGCCCT
+ATACCGATGAACCGAACCTGAATCTGTTACGCACTGAATTGCAGGAACGCTGGGGACCGGTCAATCAGGC
+TGATGGCTTTGCCGTGACAGTGCTGTCCGGCACGTATGGGGACATTTCCACGTTTGGTGTCAGCCGTAAT
+GACCATCTGATTTCCTGTATGGGGATTGCCGGTGCACCGGAACCGTCATATCTGTACGCCGCCACACTGT
+GTGCCGTTGCCAGCCAGGCGCTTTCCATCGACCCGGCGCGTCCACTCCAGACGCTGACGTTGCCCGGAAG
+AATGCCGCCTGCGGTGGGGGATCGTTTCACCTGGTCAGAACGTAATGCGCTGCTGTTTGACGGCATCTCC
+ACGTTTAACGTGAATGATGGTGGTGAAATGCAGATTGAACGCATGATCACGATGTACCGCACAAACAAGT
+ACGGTGACAGTGATCCGTCTTATCTGAACGTGAATACCATCGCCACGCTGAGTTATCTGCGTTATTCGCT
+GCGAACCCGCATCACGCAGAAATTCCCGAACTACAAGCTGGCAAGTGATGGCACCCGCTTTGCCACCGGT
+CAGGCCGTGGTGACGCCATCCGTGATCAAAACGGAGCTGCTGGCACTGTTTGAAGAATGGGAAAACGCCG
+GACTGGTCGAGGATTTCGACACGTTCAAAGAGGAGCTGTATGTGGCACGTAACAAGGACGACAAAGACCG
+TCTTGATGTGCTGTGCGGCCCGAATCTGATTAACCAGTTCCGCATTTTCGCGGCACAAGTTCAGTTCATT
+CTGTAAGGAGCATTTATGGCTGGAAATCAGCGTCAGGGGGTGGCGTTCATCCGTGTCAATGGCATGGAGC
+TTGAATCAATGGAAGGTGCCTCCTTCACGCCTTCCGGCATCACCCGTGAAGAAGTGACCGGCTCGCGGGT
+TTATGGCTGGAAAGGTAAACCTCGTGCCGCAAAAGTGGAATGCAAAATTCCGGGCGGTGGTCCCATCGGG
+CTGGATGAAATTATCGACTGGGAAAACATCACCGTCGAATTCCAGGCTGATACCGGTGAAACCTGGATGC
+TGGCGAATGCCTGGCAGGCGGATGAACCGAAAAACGACGGCGGCGAAATTTCGCTGGTACTGATGGCAAA
+ACAAAGCAAACGCATTGCATAAGGGGAAACAATGGACGAAATGAATTTAGGTCCTGAAGCACAGGAACTG
+CATGACAGCATTGTGGCAGAAATTCAGTCCGGCGTGCTGAAACTGAAAGACGGCCTGCCGTTCGGCACCG
+GTGACGAGACTGAAATGCAGTATGACGTGACGCTGCGTGAACTGACCGCAGGCGATATGATTGATGCACA
+GGCGGCTGCTGAAAAGCTGGTAATGAGCAAGGAAGGTCCGGTGCTGGTCAGTTCCCCGTCCCGGATGGGA
+CTGGAAATGCTGCGCCGACAGATTGCCAGCGTGGGCTGCATCAAAGGCCCGTTGTCGATGGCGCTGATTC
+GTAAACTGTCTGTCGATGACTTCCAGCGTCTGTCGCTGGCCACAGAAATGTACGACATGGCTGTGGCGGC
+ATCGCTGACACAAGAACGGGGGCGAGTGGCTGCGGTGCCGGAATGATATTGAGAAAGCGGCGACAGCGAT
+TGGCGTTATTCTGAAAAGTGGCCCGGAATGGGCCTTGTCTCTCCCGCTGTCCCGCTTTTTCCGGCACTGC
+CAGCAGGCTAAAACCCTCTCTCAATATCACCGTTAAATCAGGAAATATCTATGACCGGGAAACGCTTAAA
+GGCGTCTGTCATTATTGATCTTAATGGCAATCTTTCCCGGCGTTCCCGCCAGTATTCGAACCAGATAAAC
+GCCCTGTCCCGTAGCGGGCAAAGTTCCCTTCGTGCCCTGCGTATGGAGGTTGTGCGCGTTTCTGGTGCCA
+TTGACAGAATGGGTTCACTGTCAACCCGTACATTCCGAATGCTGTCAGCCGGGGCGCTGGGTATCGCTGG
+CGTGGGTTACACCGCCAATAAACTGTTTATTGGTGCAGCCGCCCAGCGTGAGCAGCAGATCATCGCCATG
+AACTCGCTGTATCACGGCGATAAGGTCAGAGCGCAGGCCATGATGGCCTGGGCGAAGCAGAACGCGAAGG
+ACACCACGTGGGGGCTGAGTGGTGTTCTGGATGAGATCCGTTCGTCGAAAGGCTTCGGCATGACGGATGA
+ACAGACGAAACAGTTCATCACCATGTTGCAGGATCAGGGGGCCATGCACGGCTGGGATTTACCCACTGCA
+CAGGGTGCCTCACTGCAACTGAAACAGATGTTTGCCCGCCAGCAAATCACAGCGGCGGATGCCAACCTGC
+TGACCGGTTACGGTATCAACGTTTATCAGGCGCTGGCGGATGCAACGGGAACGGACGTTAAAAAAATCCG
+TGATCTGGGTACAAAGGGCAAGCTGGGCATGAAATCCATTCTGACGGTATTCAGAACGCTGTCAGAACAG
+TCAAAAGGTGCACAGGCCAGTGCGATGAACTCCTGGGACGGGATGTTCGCCCAGATGGAAGCCAACCTGC
+TTGAATTTCGCATAAAGGTGGCAAACAGCGGCCCCTTTGAAGAAATCAAGAACGAGATGCGCCGGGTGCT
+TAACTGGCACGACATGGCGGATAAATCCGGGGAACTTGACGCACTGGCAGAAAACATTGGTCAGAAATTT
+CTGACCACGTTCAGAACGGTAAAAATCTCGGCGCAGGAATTATGGCGCTGGCTGAAACCGGGTAAAGATG
+CGCTGGCATGGGTTGACCAGAATATTGTCAGCCTGAAAAAACTGGCTGCTGTTCTGGTGTCTGTCTGGCT
+TGCCAATAAAGCCCTGAGAGCAGGCTGGGCCGTGGCAAAACCCTCATGGCAGGTTGCCAGTTATCCGTTT
+AAAACCGGGCGTCGTATGTGGCGCTGGATGCGAAACCGCAAACGTGGGCAGGCAGGTCTGCCGGTCCCGG
+ATGCCATGACGTCTGAGACGCTGTTGCAGGGTATCGGCATTCAGCGTGTGTTTGTCATCAACTGGCCCCG
+TGGATTTGGTGACTACGGGAGTGGCGGCGGTCGTCGTGTACGGAGCGGCGGAAGAATGGCCCCGCTGTTA
+CCCCGCCAGCCGTTATTGCTGTCCGGGCCACAGCCGCTGGCATTACCTGCACCACGCCCTGTACTGGCAT
+TACCCCCACCCGGCGTACCGGTAACGGCACGGCCTGCACCATTACCTTTACCCGGTAAATCCGGTCTTCT
+GAGCAGGCTTGCAGGCAGTGCTGCCGGGCAACTGGTTACGGGAACGGTCGGAAAGCTGGCTGATGCCGGG
+CGTGCCGTTGGCGGGTGGTTTTCCGGTATCGGAAACAAACTTGCAGGCAGTGCGATCGGTCGGGTTGTGA
+CAAAAGGTGCCGGGGCGCTGGGCTGGATGGGGAAAGGTGCCGGTCGTGCGTTGTCACGTCTGGGGGGCCC
+GGTAATGGGGGCACTCCAGCTTGCCCCCGTCCTGATGGATGAGCAGGCGTCAACCCATGAAAAAGCAGGC
+GCAATTGGCAGTACAGCCGGTGCATGGCTCGGCGGTGCCGTTGGCAGCCTTGCCGGACCGCTGGGTACGG
+TTGCTGGTGCCACGCTGGGCAGTGTCGCCGGGGAGTATCTGGGCGGTTTTGTAACCGACCTGTATCAGAA
+ATGGACGGCCACGGATAAGGAACCGCAGGAACAAAAAGTCAATGCGGAAGCCTCGCTGCGCGTCGAACTC
+GGCGAGGGGTTACGTCTGACCAGTTCCCGCGTCACCGAGGATGGTATGGGGCTGAATATTTACGCGGGCG
+ATAACTACATTACGGGCTGGTAAGACCATGTTTGAAGATGCTTTAAATGCCGTTAATGCTGTCCGGGATA
+AAACCGGTGGAGGCAGGAAAACAACCGGCAAAGGCACGTTCCGTAACGTGCCGTTTCTCGTCATCGAGGA
+GCAAAAACAGGCTGGCGGACGTCGCCTGGTTAAACGCGAGTACCCGTTACGTGATACCGGCGGCGTCAAT
+GACCTGGGGAAAAAGCTTCGCTCCCGTACATTCAGCGCCTGCATTCTGAACAGCAACGCAGAAACAGCCA
+GAGATGAAGCGGGTGCGCTGATGGATGCTCTTGATGCTCCGGGTAGCGGTGAGCTGGTACATCCTGATTT
+CGGCACTGTGGACGTCATGGTGGATTCATGGGAATGCCGCACTAAAGCGGATGAACTGAATTATTACGCG
+TTCACCGTTACCGTTTATCCGTCGTTGCAGGATACTGCCCCGGACGCAGAGACAGACACCAGTGCAGCCG
+TACCGGCACAGGCCGTTGCTGTAACCGGTTCTCTGGGAGATACGCTGTCCTCTGTCTGGCAAACCGTAAA
+AGATGGCACTGCGGCGGCAACCGCCGTGATGGAAGCTGTAACCGGTGTCATCGATGATATCAGTGATGCG
+GTGGACAATCTGGGGGTTACGCAGACTGTCAGCGGTCTGATGGGATCGCTTTCTGCGATGAAAGGCTCTG
+TGACCAGCCTGATTAACCAGCCTGCCATGCTGGCCTCCTCGCTGATGGGGGCGCTGTCCGGCGTTTCATC
+GTTATGCGATACCCGGACAGCATTTTCCACATGGAACCGTCTGGCGCAGCGATTCGAACGTCGCCATGCC
+GCCACCGCAGGCAGACAGGGGACAATCACAACCTCGTACAACAGTCCGGTTGCAGAAAAAAATATTGCCA
+CACTGAACTACGTCATGCTGGCAGCGGCGCAGACATACCGGGCAGAAGCTGCCAGCCAGGCACTGACTGC
+GGCACTGGATTTCAGTCGCCGGATGGATAATGCCGCCCGTGCACCTGTACTGGATGCCCCGTCCACCACA
+ACCGGCACAGCCAGCGGGGCCAGCAGCACATCTGCTACCGTCACACAGGGACAGTTACAGTTAACTGCCA
+TAACCCCGGACGGCGGCTTTTCACAGGTATCCTTTTCAGACAGTGGTACAGCCACGCCCCCGGTATTTGA
+AAGTGTGTCCGATATCGAAAAAACCACTGCCATGCTGGGGGCGGCGCTGGATAGCGTCATTCTGACGGCA
+TCTGAGCAGGGTTTTTCGACAGACAGTGTTCAGCTTACGCAACTGCGTCTGCTGGTTGTTGCCGACCTGG
+AAAAACGCGGGCTGCAACTGGCGGGTAGTGAATCACACCACCTGCCAGAAACGCTCCCGGCAATGGTTGC
+ACTGTACCGGTTCACCGGAAACAGCCGGAACTGGCAACGGCTGGCCCGCAGGAACGGTATCAGCAACCCG
+TTATTTGTTCCCGGTGGTGTCAGTATTGAGGTGATTAATGAGTAATACCGTCACACTGCGAGCGGATGGC
+AGGCTGTTTACCGGCTGGACGTCAGTCTCTGTCACCCGCTCGATTGAATCCGTAGCCGGATATTTTGAGC
+TGGGGGTGAACGTGCCACCGGGCACGGATTTATCCGGGCTGGCTCCGGGGAAGAAGTTCACGCTGGAAAT
+CGGGGGGCAGATTGTCTGCACCGGTTATATCGATTCACGGCGACGCCAGATGACCGCTGACAGTATGAAA
+ATCACTGTCGCCGGACGTGACAAAACGGCTGACCTGATTGACTGTGCTGCCGTTTACAGTGGCGGACAGT
+GGAAAAACCGCACACTGGAGCAGATTGCGCGTGACCTGTGCGCTCCTTATGGCGTTACCGTTCGCTGGGA
+GCTTTCCGATAAGGAAAGTTCGGCAGCTTTTCCCGGCTTCACGCTGGACCATTCAGAAACCGTTTATGAG
+GCGCTGGTGCGTGCCTCCCGCGCACGCGGTGTACTGATGACCAGCAATGCCGCCGGAGAGCTGGTATTCA
+GCCGGGCTGCCAGCACAGCCACTGATGAGCTGGTTCTCGGAGAAAATCTGCTGACACTGGATTTTGAGGA
+AGACTTCCGCGACCGGTTCAGCGAATACACCGTCAAGGGGTATGCCCGCGCAAATGGTGCTGAGGGTGAT
+GATATTGATGCGAAAAGTATCGTATCCCGGAAAGGGACCGCCACTGACAGTGATGTGACCCGTTACAGAC
+CGATGATCATCATTGCTGACAGCAAGATTACGGCGAAGGATGCACAGGCCCGCGCCCTGCGTGAGCAACG
+CCGCAGACTGGCAAAATCCATCACCTTTGAGGCAGAAATTGACGGATGGACTCGCAAGGACGGGCAACTC
+TGGATGCCGAACCTGCTGGTCACTATTGATGCCTCGAAATATGCCATCAAAACCACGGAATTACTGGTCA
+GCAAAGTCACCCTGATACTGAATGACCAGGACGGGCTGAAAACCCGCGTCAGCCTTGCACCACGCGAAGG
+CTTTCTGGTGCCGGTTGAAAGCGACCGTAAAAACAGGAAAGGCGGCGACAGTAACGGCGGTATTGATGCG
+CTGGTTGAAGATTATTATCGCAGACACCCGGAGAAAACGCCGCCGTGGAAAGAGTAAATGATTCCGCCTT
+GAACCGCCTGCTGACGCCGCTGATGCGTCGTGTGCGCCTGATGCTTGCGCGCGCTGTTGTTAACGTGATT
+AACGACGGGCGAAAGGTTCAGAACCTGCAGGTCGGTCTGCTGGATGATGAGGAATCCGATGAAGTGGAGC
+GCCTGCAAAATTACGGGCATTTCAGCGTTCCCCTGCCGGGCGCAGAGGCGCTGATTGCCTGTGTAGGCGC
+ACAACGTGATCAGGGGATTGCTGTTGTGGTGGAAGACCGCCGCTACCGCCCGACAAATCTTGAACCGGGT
+GATGCAGGCATTTACCACCACGAGGGGCATCGTATCAGGCTGACAAAGGACGGACGCTGCATCATTACCT
+GTAAAACGGTTGAGGTTTACGCTGATGAAAGTATGACCGTTGACACACCCAGAACCACGTTTACCGGCGA
+CGTTGAGATCCAGAAAGGTCTGGGCGTTAAAGGTAAAAGCCAGTTCGACAGCAATATTACTGCCCCGGAT
+GCCATCATCAATGGCAAATCGACGGATAAGCATATCCACCGTGGCGACAGCGGCGGAACCACAGGGCCGA
+TGCAATGACCGATTTAGCCATTATCTGGACGAACGGACGCGGCGATATTGCGCAGGATGGTATTGATATG
+CTGACCGACGACAGCCTGACAACCGATGTGACAATCTCTCTGTTTACCGACCGGCGCGCGCTGGATTCTG
+ACACGCTGCCGGATGGTTCAGATGATCGCCGTGGATGGTGGGGTGACAGTTACCGCGACCGCCCCATCGG
+TTCGCGGTTGTGGCTGTTATCACGTGAAAAAGCCACGCCGGATACGCTGGAACGCGCCAGAGGGTATGCC
+GAAGAGGCGCTGGAATGGCTGAAAACAGCGGGCCGGGTAAGTGCGATTAACGTCAGAGCGGAACAGTTAC
+ATCAGGGCTGGTTATACCTCTACATTGCACTGACATTACCGGATGGTTCCGTTATTCCTTATGAGTTTAA
+AGCAGCATTTAACGGGGTTTAAATGGCTTATTCACCACCGACATTATCATCGCTGATTGCCCGTACAGAA
+CAGAATATTGAACAGCGCCTGCCGGGTAGCTGGCCTCAGGCCCGTGAAAAAACGCTGAGTGCCATTGCTT
+ATGCTCAGGCGGGCCTTGCTGCCGGTTGTCACGAGCATATTTCATGGGTTGGACGGCAGATTATCCCGTC
+GACAGCAGATGAAGATGAGTTGCTGGAGCACTGCCGGTTCTGGGGCGTGCGCCGCAAACAGGCGACAGCC
+GCCAGCGGCCCGCTGACTGTCACCACATCGGCAGCGACCACCATTCCTGCCGGTACACGCTGGCAGCGTG
+CTGATGGTGTGGTTTACAGCCTGGCTGATACCATTGTGATTGACCGTGCAGGAACGACGGAAATTACCGT
+TACCGCACTGGCTGCCGGTGAAGCAGGAAATACCGGTGAGAATACCCTTTTAACGTTGATCACCCCGGTT
+GCCTGTGTTGTTTCCGATGCCATCACTGTAAAAGGGTTTTCCGGTGGAGCTGATATTGAGAGTGCAGCGG
+AGCTGCTGTCACGGCTGGAATATCGTGTCCAGTATCCTCCGTTCGGCGGTAATCAGTTTGATTACGTTCG
+CTGGGCACGTGAAGTCAGCGGTGTTACCCGTGCCTGGTGTTTTCCGACATGGAAAGGCGGTGGCACAGTC
+GGGGTGACGTTTGTTATGGATAACCGGAGCAATATTTTTCCGCAACCGGCAGACGTGGAACGCGTGGCGG
+ATTATATCGCCGGTCATACTGACCCGATCACTGGTCTGATTGTCGGACAGCCTGACGGTGTAAATGTCAC
+GGTATTTGCGCCAAAGGCAAAGCCGGTAAATCCACGGATTTATATATCACCGAAGACAGCCGAACTGAAA
+CAGGCTATTACCAACGCCATTAATACCATGTTTTTTAATGAGGTGATGCCGGGCGGCGCACTTGCCCCCT
+CCCGTATTATCCGTGCGGTGGCAGGTGTTACCGGTCTGGATGATTTTGAAGTGCGTTTCCCGACAGAGAT
+CCAGCGTTCGGAGAATACGGAACTCTTAACAGCGGGGACAATTGAATGGCTGTAACACCCTGGCAGACGG
+CCTTTCTGCAATTACTGCCGTCAGGGCTTGCCTGGAATAAAAGCCCCGACAGCAAATTATCTGCGCTGGC
+GCAGGCCATCAGCGACGTGATTGCCACTGCGGCGGATGATGCGCGGCAAATGCTGCGGGAGCGTTTCCCG
+TCCACATCCCGCTGGTATCTGGGGGAGTGGGAATCATTTCTGGGGTTGCCGGACTGTACCAGCGAAAACG
+GCACCCTGTCCGAACGCCAGCGGGCTGCCGCGAATAAAATGCGTATGACCGGCAATCTGAGTCGGCGCTT
+TTATGAATGGCTGGCTGCGCAGTACGGTTTTACCGTCAGGCTGACGGATTCCACAGAAGGCCAGTGGGTT
+ACGCAGGTCAATATTTACGGTATTAAAAATTATCGCAACGCAACGGTGCTGGATAATGTTCTGACGCCGT
+TACGTGTTTATGAATCGGGTGCGCTGGAATGTTTACTGGAGAAATATAAACCCGCGCATCAGATTTATAA
+ATTTGTTTACCATGACGGAGATAACTAATGTTTTATATTGATAACGACAGCGGCGTAACCGTCATGCCGC
+CCGTATCCGCCCAGCGTAGTGCTATCGTTCGCTGGTTTTCAGAAGGTGACGGGAATAATGTTATCACATG
+GCCCGGCATGGACTGGTTTAATATTGTGCAGGCGGAGTTATTAAACACGCTGGAAGAAGCCGGTATTCAA
+CCGGATAAAACAAAATTAAACCAGCTTGCACTGTCCATTAAAGCCATTATGAGCAATAACGCGCTGCTGA
+TAAAAAATAACCTCAGCGAAATTAAAACTGCCGGGGCATCAGCACAGCGTACAGCACGTGAAAATCTGGA
+TATCTATGATGCCAGCCTGAACAAAAAAGGACTCGTTCAGCTAACCAGTGCCACTGACAGCCCCAGTGAA
+ACGCTGGCAGCCACCGCAAAAGCGGTGAAAATTGCAATGGATAATGCCAATGCCCGTCTGGCAAAAGACC
+GGAACGGAGCAGATATTCCCAATAAGCCGCTGTTTATCCAAAACCTCGGTTTACAGGAAACGGTAAACAG
+GGCTAGGAACGCCGTGCAAAAGAATGGCGATACCTTGTCCGGTGGGCTTACTTTTGAAAACGACTCAATC
+CTTGCCTGGATTCGAAATACTGACTGGGCAAAGATTGGATTTAAAAATGATGCCGACAGCGACACTGATT
+CATACATGTGGTTTGAAACAGGCGACAACGGCAATGAATATTTCAAATGGAGAAGCAAACAAAGCACCAC
+AACAAAAGACCTGATGAATCTTAAATGGGATGCTTTGTCTGTTCTTGTCAATGCC</t>
+  </si>
+  <si>
+    <t>Enterobacteria phage Mu</t>
+  </si>
+  <si>
+    <t>NC_000929.1</t>
+  </si>
 </sst>
 </file>
 
@@ -24015,11 +24480,11 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="20% - Accent1" xfId="3" builtinId="30"/>
@@ -24030,54 +24495,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="24">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.749992370372631"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="3" tint="0.749992370372631"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -24196,6 +24613,54 @@
         <horizontal style="thin">
           <color indexed="64"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.749992370372631"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3" tint="0.749992370372631"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -24858,11 +25323,11 @@
     <tableColumn id="11" xr3:uid="{5B511061-18A2-4ED7-BF00-1F9D0D03CDD2}" name="Protein Type" dataDxfId="7"/>
     <tableColumn id="12" xr3:uid="{1CC377FB-E0DF-4ECD-92C5-447D8E00B72F}" name="Annotation" dataDxfId="6"/>
     <tableColumn id="13" xr3:uid="{6218B8FC-0FB8-4D5F-AC0D-A90EF22B62FD}" name="RBP sequence (aa)" dataDxfId="5"/>
-    <tableColumn id="19" xr3:uid="{9438957F-AC15-416C-9D0C-0EB0081EC58A}" name="CleanSeq" dataDxfId="0" dataCellStyle="60% - Accent1"/>
-    <tableColumn id="18" xr3:uid="{5A87B8C6-6161-4A3F-BD1B-433725A12DDE}" name="FASTA" dataDxfId="1" dataCellStyle="60% - Accent1"/>
-    <tableColumn id="14" xr3:uid="{D986BF2F-4027-43AD-8708-BA3A437C2F4A}" name="RBP Delineation (aa)" dataDxfId="4"/>
-    <tableColumn id="16" xr3:uid="{2AA43298-5132-4CE1-8D55-C0DA57AAB82F}" name="Expression system" dataDxfId="3"/>
-    <tableColumn id="17" xr3:uid="{3B537590-5B2B-43A8-90E5-60B8CB7578EF}" name="REF" dataDxfId="2"/>
+    <tableColumn id="19" xr3:uid="{9438957F-AC15-416C-9D0C-0EB0081EC58A}" name="CleanSeq" dataDxfId="4" dataCellStyle="60% - Accent1"/>
+    <tableColumn id="18" xr3:uid="{5A87B8C6-6161-4A3F-BD1B-433725A12DDE}" name="FASTA" dataDxfId="3" dataCellStyle="60% - Accent1"/>
+    <tableColumn id="14" xr3:uid="{D986BF2F-4027-43AD-8708-BA3A437C2F4A}" name="RBP Delineation (aa)" dataDxfId="2"/>
+    <tableColumn id="16" xr3:uid="{2AA43298-5132-4CE1-8D55-C0DA57AAB82F}" name="Expression system" dataDxfId="1"/>
+    <tableColumn id="17" xr3:uid="{3B537590-5B2B-43A8-90E5-60B8CB7578EF}" name="REF" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -25186,28 +25651,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11298BA3-887D-4755-9723-7AB39BB5F3E6}">
   <dimension ref="A1:U98"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.140625" customWidth="1"/>
-    <col min="3" max="3" width="31.5703125" customWidth="1"/>
-    <col min="4" max="4" width="22.85546875" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" customWidth="1"/>
-    <col min="6" max="6" width="18.42578125" customWidth="1"/>
-    <col min="7" max="7" width="35.28515625" customWidth="1"/>
-    <col min="8" max="8" width="23.85546875" customWidth="1"/>
-    <col min="9" max="9" width="25.7109375" customWidth="1"/>
-    <col min="10" max="10" width="24.28515625" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.109375" customWidth="1"/>
+    <col min="3" max="3" width="31.5546875" customWidth="1"/>
+    <col min="4" max="4" width="22.88671875" customWidth="1"/>
+    <col min="5" max="5" width="18.33203125" customWidth="1"/>
+    <col min="6" max="6" width="18.44140625" customWidth="1"/>
+    <col min="7" max="7" width="35.33203125" customWidth="1"/>
+    <col min="8" max="8" width="23.88671875" customWidth="1"/>
+    <col min="9" max="9" width="25.6640625" customWidth="1"/>
+    <col min="10" max="10" width="24.33203125" customWidth="1"/>
     <col min="11" max="11" width="22" customWidth="1"/>
-    <col min="12" max="12" width="23.28515625" customWidth="1"/>
-    <col min="13" max="13" width="17.7109375" customWidth="1"/>
-    <col min="14" max="16" width="21.7109375" customWidth="1"/>
-    <col min="17" max="17" width="23.28515625" customWidth="1"/>
-    <col min="18" max="18" width="25.28515625" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" customWidth="1"/>
-    <col min="20" max="20" width="13.7109375" customWidth="1"/>
-    <col min="21" max="21" width="34.28515625" customWidth="1"/>
-    <col min="22" max="22" width="17.140625" customWidth="1"/>
+    <col min="12" max="12" width="23.33203125" customWidth="1"/>
+    <col min="13" max="13" width="17.6640625" customWidth="1"/>
+    <col min="14" max="16" width="21.6640625" customWidth="1"/>
+    <col min="17" max="17" width="23.33203125" customWidth="1"/>
+    <col min="18" max="18" width="25.33203125" customWidth="1"/>
+    <col min="19" max="19" width="14.44140625" customWidth="1"/>
+    <col min="20" max="20" width="13.6640625" customWidth="1"/>
+    <col min="21" max="21" width="34.33203125" customWidth="1"/>
+    <col min="22" max="22" width="17.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="19" customFormat="1">
@@ -25227,10 +25692,10 @@
         <v>147</v>
       </c>
       <c r="F1" s="11" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="G1" s="11" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H1" s="11" t="s">
         <v>154</v>
@@ -25254,10 +25719,10 @@
         <v>151</v>
       </c>
       <c r="O1" s="11" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="P1" s="11" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="Q1" s="11" t="s">
         <v>153</v>
@@ -25272,7 +25737,7 @@
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="21" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B2" s="22" t="s">
         <v>13</v>
@@ -25287,7 +25752,7 @@
         <v>59</v>
       </c>
       <c r="F2" s="22" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G2" s="22" t="s">
         <v>236</v>
@@ -25299,7 +25764,7 @@
         <v>72917</v>
       </c>
       <c r="J2" s="22" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="K2" s="22" t="s">
         <v>20</v>
@@ -25308,16 +25773,16 @@
         <v>44</v>
       </c>
       <c r="M2" s="25" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="N2" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="O2" s="67" t="s">
-        <v>612</v>
-      </c>
-      <c r="P2" s="67" t="s">
-        <v>645</v>
+      <c r="O2" s="66" t="s">
+        <v>611</v>
+      </c>
+      <c r="P2" s="66" t="s">
+        <v>644</v>
       </c>
       <c r="Q2" s="25">
         <v>851</v>
@@ -25326,13 +25791,13 @@
         <v>45</v>
       </c>
       <c r="S2" s="27" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="U2" s="7"/>
     </row>
     <row r="3" spans="1:21">
       <c r="A3" s="21" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B3" s="22" t="s">
         <v>14</v>
@@ -25347,7 +25812,7 @@
         <v>59</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G3" s="22" t="s">
         <v>237</v>
@@ -25373,11 +25838,11 @@
       <c r="N3" s="26" t="s">
         <v>135</v>
       </c>
-      <c r="O3" s="67" t="s">
-        <v>613</v>
-      </c>
-      <c r="P3" s="67" t="s">
-        <v>646</v>
+      <c r="O3" s="66" t="s">
+        <v>612</v>
+      </c>
+      <c r="P3" s="66" t="s">
+        <v>645</v>
       </c>
       <c r="Q3" s="25">
         <v>133</v>
@@ -25392,7 +25857,7 @@
     </row>
     <row r="4" spans="1:21">
       <c r="A4" s="21" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B4" s="25" t="s">
         <v>15</v>
@@ -25407,7 +25872,7 @@
         <v>59</v>
       </c>
       <c r="F4" s="25" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G4" s="25" t="s">
         <v>238</v>
@@ -25419,13 +25884,13 @@
         <v>39699</v>
       </c>
       <c r="J4" s="25" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="K4" s="25" t="s">
         <v>73</v>
       </c>
       <c r="L4" s="25" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="M4" s="25" t="s">
         <v>98</v>
@@ -25433,11 +25898,11 @@
       <c r="N4" s="25" t="s">
         <v>113</v>
       </c>
-      <c r="O4" s="67" t="s">
+      <c r="O4" s="66" t="s">
         <v>113</v>
       </c>
-      <c r="P4" s="67" t="s">
-        <v>647</v>
+      <c r="P4" s="66" t="s">
+        <v>646</v>
       </c>
       <c r="Q4" s="25">
         <v>1064</v>
@@ -25446,13 +25911,13 @@
         <v>45</v>
       </c>
       <c r="S4" s="27" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="U4" s="7"/>
     </row>
     <row r="5" spans="1:21">
       <c r="A5" s="21" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>16</v>
@@ -25467,7 +25932,7 @@
         <v>60</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G5" s="22" t="s">
         <v>239</v>
@@ -25488,16 +25953,16 @@
         <v>44</v>
       </c>
       <c r="M5" s="22" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="N5" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="O5" s="67" t="s">
-        <v>614</v>
-      </c>
-      <c r="P5" s="67" t="s">
-        <v>648</v>
+      <c r="O5" s="66" t="s">
+        <v>613</v>
+      </c>
+      <c r="P5" s="66" t="s">
+        <v>647</v>
       </c>
       <c r="Q5" s="25">
         <v>259</v>
@@ -25512,7 +25977,7 @@
     </row>
     <row r="6" spans="1:21">
       <c r="A6" s="21" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B6" s="22" t="s">
         <v>16</v>
@@ -25527,7 +25992,7 @@
         <v>60</v>
       </c>
       <c r="F6" s="22" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G6" s="22" t="s">
         <v>239</v>
@@ -25548,16 +26013,16 @@
         <v>44</v>
       </c>
       <c r="M6" s="22" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="N6" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="O6" s="67" t="s">
-        <v>615</v>
-      </c>
-      <c r="P6" s="67" t="s">
-        <v>649</v>
+      <c r="O6" s="66" t="s">
+        <v>614</v>
+      </c>
+      <c r="P6" s="66" t="s">
+        <v>648</v>
       </c>
       <c r="Q6" s="25">
         <v>184</v>
@@ -25572,7 +26037,7 @@
     </row>
     <row r="7" spans="1:21">
       <c r="A7" s="21" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B7" s="22" t="s">
         <v>16</v>
@@ -25587,7 +26052,7 @@
         <v>60</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G7" s="22" t="s">
         <v>239</v>
@@ -25608,16 +26073,16 @@
         <v>44</v>
       </c>
       <c r="M7" s="22" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="N7" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="O7" s="67" t="s">
-        <v>616</v>
-      </c>
-      <c r="P7" s="67" t="s">
-        <v>650</v>
+      <c r="O7" s="66" t="s">
+        <v>615</v>
+      </c>
+      <c r="P7" s="66" t="s">
+        <v>649</v>
       </c>
       <c r="Q7" s="25">
         <v>498</v>
@@ -25632,7 +26097,7 @@
     </row>
     <row r="8" spans="1:21">
       <c r="A8" s="21" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B8" s="22" t="s">
         <v>17</v>
@@ -25647,7 +26112,7 @@
         <v>60</v>
       </c>
       <c r="F8" s="22" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G8" s="22" t="s">
         <v>240</v>
@@ -25673,11 +26138,11 @@
       <c r="N8" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="O8" s="67" t="s">
-        <v>617</v>
-      </c>
-      <c r="P8" s="67" t="s">
-        <v>651</v>
+      <c r="O8" s="66" t="s">
+        <v>616</v>
+      </c>
+      <c r="P8" s="66" t="s">
+        <v>650</v>
       </c>
       <c r="Q8" s="25">
         <v>181</v>
@@ -25692,7 +26157,7 @@
     </row>
     <row r="9" spans="1:21">
       <c r="A9" s="21" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B9" s="22" t="s">
         <v>18</v>
@@ -25707,7 +26172,7 @@
         <v>60</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G9" s="26" t="s">
         <v>174</v>
@@ -25733,11 +26198,11 @@
       <c r="N9" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="O9" s="67" t="s">
-        <v>618</v>
-      </c>
-      <c r="P9" s="67" t="s">
-        <v>652</v>
+      <c r="O9" s="66" t="s">
+        <v>617</v>
+      </c>
+      <c r="P9" s="66" t="s">
+        <v>651</v>
       </c>
       <c r="Q9" s="25">
         <v>124</v>
@@ -25752,7 +26217,7 @@
     </row>
     <row r="10" spans="1:21">
       <c r="A10" s="21" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B10" s="22" t="s">
         <v>19</v>
@@ -25767,7 +26232,7 @@
         <v>60</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G10" s="22" t="s">
         <v>241</v>
@@ -25793,11 +26258,11 @@
       <c r="N10" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="O10" s="67" t="s">
-        <v>619</v>
-      </c>
-      <c r="P10" s="67" t="s">
-        <v>653</v>
+      <c r="O10" s="66" t="s">
+        <v>618</v>
+      </c>
+      <c r="P10" s="66" t="s">
+        <v>652</v>
       </c>
       <c r="Q10" s="25">
         <v>205</v>
@@ -25812,7 +26277,7 @@
     </row>
     <row r="11" spans="1:21">
       <c r="A11" s="21" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B11" s="25" t="s">
         <v>37</v>
@@ -25827,7 +26292,7 @@
         <v>109</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G11" s="22" t="s">
         <v>242</v>
@@ -25853,11 +26318,11 @@
       <c r="N11" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="O11" s="67" t="s">
-        <v>620</v>
-      </c>
-      <c r="P11" s="67" t="s">
-        <v>654</v>
+      <c r="O11" s="66" t="s">
+        <v>619</v>
+      </c>
+      <c r="P11" s="66" t="s">
+        <v>653</v>
       </c>
       <c r="Q11" s="25">
         <v>80</v>
@@ -25872,7 +26337,7 @@
     </row>
     <row r="12" spans="1:21">
       <c r="A12" s="21" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B12" s="25" t="s">
         <v>41</v>
@@ -25887,7 +26352,7 @@
         <v>59</v>
       </c>
       <c r="F12" s="22" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G12" s="22" t="s">
         <v>243</v>
@@ -25899,7 +26364,7 @@
         <v>44385</v>
       </c>
       <c r="J12" s="25" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="K12" s="25" t="s">
         <v>42</v>
@@ -25908,16 +26373,16 @@
         <v>44</v>
       </c>
       <c r="M12" s="25" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="N12" s="26" t="s">
         <v>133</v>
       </c>
-      <c r="O12" s="67" t="s">
-        <v>621</v>
-      </c>
-      <c r="P12" s="67" t="s">
-        <v>655</v>
+      <c r="O12" s="66" t="s">
+        <v>620</v>
+      </c>
+      <c r="P12" s="66" t="s">
+        <v>654</v>
       </c>
       <c r="Q12" s="25">
         <v>1089</v>
@@ -25926,58 +26391,58 @@
         <v>45</v>
       </c>
       <c r="S12" s="27" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="U12" s="7"/>
     </row>
     <row r="13" spans="1:21">
       <c r="A13" s="30" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B13" s="31" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D13" s="30" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E13" s="31" t="s">
         <v>109</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H13" s="31" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="I13" s="32">
         <v>41116</v>
       </c>
       <c r="J13" s="31" t="s">
+        <v>472</v>
+      </c>
+      <c r="K13" s="31" t="s">
         <v>473</v>
       </c>
-      <c r="K13" s="31" t="s">
-        <v>474</v>
-      </c>
       <c r="L13" s="31" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="M13" s="31" t="s">
+        <v>478</v>
+      </c>
+      <c r="N13" s="31" t="s">
         <v>479</v>
       </c>
-      <c r="N13" s="31" t="s">
-        <v>480</v>
-      </c>
       <c r="O13" s="64" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="P13" s="64" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="Q13" s="31">
         <v>810</v>
@@ -25986,59 +26451,59 @@
         <v>45</v>
       </c>
       <c r="S13" s="33" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="T13" s="9"/>
       <c r="U13" s="7"/>
     </row>
     <row r="14" spans="1:21">
       <c r="A14" s="30" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B14" s="32" t="s">
+        <v>499</v>
+      </c>
+      <c r="C14" s="31" t="s">
         <v>500</v>
       </c>
-      <c r="C14" s="31" t="s">
-        <v>501</v>
-      </c>
       <c r="D14" s="30" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E14" s="31" t="s">
         <v>109</v>
       </c>
       <c r="F14" s="31" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G14" s="31" t="s">
+        <v>501</v>
+      </c>
+      <c r="H14" s="31" t="s">
         <v>502</v>
-      </c>
-      <c r="H14" s="31" t="s">
-        <v>503</v>
       </c>
       <c r="I14" s="32">
         <v>40163</v>
       </c>
       <c r="J14" s="31" t="s">
+        <v>503</v>
+      </c>
+      <c r="K14" s="31" t="s">
         <v>504</v>
-      </c>
-      <c r="K14" s="31" t="s">
-        <v>505</v>
       </c>
       <c r="L14" s="31" t="s">
         <v>44</v>
       </c>
       <c r="M14" s="32" t="s">
+        <v>505</v>
+      </c>
+      <c r="N14" s="31" t="s">
         <v>506</v>
       </c>
-      <c r="N14" s="31" t="s">
-        <v>507</v>
-      </c>
       <c r="O14" s="64" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="P14" s="64" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="Q14" s="32">
         <v>684</v>
@@ -26047,59 +26512,59 @@
         <v>45</v>
       </c>
       <c r="S14" s="33" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T14" s="9"/>
       <c r="U14" s="7"/>
     </row>
     <row r="15" spans="1:21">
       <c r="A15" s="30" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B15" s="31" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D15" s="30" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E15" s="31" t="s">
         <v>59</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G15" s="31" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H15" s="31" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I15" s="32">
         <v>41119</v>
       </c>
       <c r="J15" s="31" t="s">
+        <v>488</v>
+      </c>
+      <c r="K15" s="31" t="s">
         <v>489</v>
-      </c>
-      <c r="K15" s="31" t="s">
-        <v>490</v>
       </c>
       <c r="L15" s="31" t="s">
         <v>44</v>
       </c>
       <c r="M15" s="32" t="s">
+        <v>490</v>
+      </c>
+      <c r="N15" s="34" t="s">
         <v>491</v>
       </c>
-      <c r="N15" s="34" t="s">
-        <v>492</v>
-      </c>
       <c r="O15" s="64" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="P15" s="64" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="Q15" s="31">
         <v>576</v>
@@ -26108,20 +26573,20 @@
         <v>45</v>
       </c>
       <c r="S15" s="33" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="T15" s="9"/>
       <c r="U15" s="7"/>
     </row>
     <row r="16" spans="1:21">
       <c r="A16" s="30" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C16" s="31" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D16" s="35" t="s">
         <v>167</v>
@@ -26130,37 +26595,37 @@
         <v>59</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G16" s="31" t="s">
+        <v>522</v>
+      </c>
+      <c r="H16" s="31" t="s">
         <v>523</v>
-      </c>
-      <c r="H16" s="31" t="s">
-        <v>524</v>
       </c>
       <c r="I16" s="32">
         <v>76622</v>
       </c>
       <c r="J16" s="31" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K16" s="32" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="L16" s="31" t="s">
         <v>67</v>
       </c>
       <c r="M16" s="32" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="N16" s="31" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="O16" s="64" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="P16" s="64" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="Q16" s="32">
         <v>729</v>
@@ -26176,25 +26641,25 @@
     </row>
     <row r="17" spans="1:21">
       <c r="A17" s="30" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B17" s="32" t="s">
         <v>233</v>
       </c>
       <c r="C17" s="31" t="s">
+        <v>524</v>
+      </c>
+      <c r="D17" s="30" t="s">
         <v>525</v>
-      </c>
-      <c r="D17" s="30" t="s">
-        <v>526</v>
       </c>
       <c r="E17" s="32" t="s">
         <v>59</v>
       </c>
       <c r="F17" s="31" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G17" s="31" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H17" s="31" t="s">
         <v>206</v>
@@ -26203,25 +26668,25 @@
         <v>77554</v>
       </c>
       <c r="J17" s="31" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="K17" s="32" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="L17" s="31" t="s">
         <v>67</v>
       </c>
       <c r="M17" s="32" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="N17" s="31" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="O17" s="64" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="P17" s="64" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="Q17" s="32">
         <v>722</v>
@@ -26237,7 +26702,7 @@
     </row>
     <row r="18" spans="1:21">
       <c r="A18" s="30" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B18" s="36" t="s">
         <v>13</v>
@@ -26252,7 +26717,7 @@
         <v>59</v>
       </c>
       <c r="F18" s="36" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G18" s="36" t="s">
         <v>236</v>
@@ -26264,25 +26729,25 @@
         <v>72917</v>
       </c>
       <c r="J18" s="31" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K18" s="32" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="L18" s="32" t="s">
         <v>67</v>
       </c>
       <c r="M18" s="31" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="N18" s="31" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="O18" s="64" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="P18" s="64" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="Q18" s="32">
         <v>1063</v>
@@ -26291,20 +26756,20 @@
         <v>45</v>
       </c>
       <c r="S18" s="33" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="T18" s="9"/>
       <c r="U18" s="7"/>
     </row>
     <row r="19" spans="1:21">
       <c r="A19" s="30" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B19" s="31" t="s">
+        <v>508</v>
+      </c>
+      <c r="C19" s="31" t="s">
         <v>509</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>510</v>
       </c>
       <c r="D19" s="35" t="s">
         <v>155</v>
@@ -26313,37 +26778,37 @@
         <v>60</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H19" s="31" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="I19" s="32">
         <v>108853</v>
       </c>
       <c r="J19" s="31" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="K19" s="31" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="L19" s="31" t="s">
         <v>67</v>
       </c>
       <c r="M19" s="32" t="s">
+        <v>512</v>
+      </c>
+      <c r="N19" s="31" t="s">
         <v>513</v>
       </c>
-      <c r="N19" s="31" t="s">
-        <v>514</v>
-      </c>
       <c r="O19" s="64" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="P19" s="64" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="Q19" s="32">
         <v>585</v>
@@ -26359,7 +26824,7 @@
     </row>
     <row r="20" spans="1:21">
       <c r="A20" s="30" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B20" s="31" t="s">
         <v>41</v>
@@ -26374,7 +26839,7 @@
         <v>59</v>
       </c>
       <c r="F20" s="36" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G20" s="36" t="s">
         <v>243</v>
@@ -26386,25 +26851,25 @@
         <v>44385</v>
       </c>
       <c r="J20" s="31" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K20" s="31" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="L20" s="36" t="s">
         <v>44</v>
       </c>
       <c r="M20" s="31" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="N20" s="32" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="O20" s="64" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="P20" s="64" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="Q20" s="31">
         <v>632</v>
@@ -26413,59 +26878,59 @@
         <v>45</v>
       </c>
       <c r="S20" s="33" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="T20" s="9"/>
       <c r="U20" s="7"/>
     </row>
     <row r="21" spans="1:21" s="9" customFormat="1">
       <c r="A21" s="38" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B21" s="38" t="s">
+        <v>576</v>
+      </c>
+      <c r="C21" s="38" t="s">
+        <v>587</v>
+      </c>
+      <c r="D21" s="39" t="s">
         <v>577</v>
-      </c>
-      <c r="C21" s="38" t="s">
-        <v>588</v>
-      </c>
-      <c r="D21" s="39" t="s">
-        <v>578</v>
       </c>
       <c r="E21" s="38" t="s">
         <v>109</v>
       </c>
       <c r="F21" s="38" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="G21" s="38" t="s">
+        <v>578</v>
+      </c>
+      <c r="H21" s="40" t="s">
         <v>579</v>
-      </c>
-      <c r="H21" s="40" t="s">
-        <v>580</v>
       </c>
       <c r="I21" s="41">
         <v>168463</v>
       </c>
       <c r="J21" s="38" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="K21" s="38" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="L21" s="38" t="s">
         <v>67</v>
       </c>
       <c r="M21" s="38" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="N21" s="40" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="O21" s="64" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="P21" s="64" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="Q21" s="38">
         <v>670</v>
@@ -26480,7 +26945,7 @@
     </row>
     <row r="22" spans="1:21" s="9" customFormat="1">
       <c r="A22" s="38" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B22" s="38" t="s">
         <v>219</v>
@@ -26495,10 +26960,10 @@
         <v>109</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H22" s="40" t="s">
         <v>199</v>
@@ -26507,25 +26972,25 @@
         <v>168903</v>
       </c>
       <c r="J22" s="38" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="K22" s="38" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="L22" s="38" t="s">
         <v>67</v>
       </c>
       <c r="M22" s="38" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="N22" s="38" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="O22" s="64" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="P22" s="64" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="Q22" s="38">
         <v>659</v>
@@ -26540,52 +27005,52 @@
     </row>
     <row r="23" spans="1:21" s="9" customFormat="1">
       <c r="A23" s="38" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B23" s="39" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C23" s="38" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="E23" s="38" t="s">
         <v>109</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G23" s="38" t="s">
+        <v>594</v>
+      </c>
+      <c r="H23" s="40" t="s">
         <v>595</v>
-      </c>
-      <c r="H23" s="40" t="s">
-        <v>596</v>
       </c>
       <c r="I23" s="39">
         <v>143652</v>
       </c>
       <c r="J23" s="38" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="K23" s="38" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="L23" s="38" t="s">
         <v>67</v>
       </c>
       <c r="M23" s="38" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="N23" s="40" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="O23" s="64" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="P23" s="64" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="Q23" s="39">
         <v>458</v>
@@ -26600,52 +27065,52 @@
     </row>
     <row r="24" spans="1:21" s="9" customFormat="1">
       <c r="A24" s="38" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B24" s="38" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="C24" s="38" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E24" s="38" t="s">
         <v>109</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="G24" s="38" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H24" s="40" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I24" s="39">
         <v>167920</v>
       </c>
       <c r="J24" s="38" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="K24" s="38" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="L24" s="38" t="s">
         <v>67</v>
       </c>
       <c r="M24" s="38" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="N24" s="40" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="O24" s="64" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="P24" s="64" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="Q24" s="39">
         <v>166</v>
@@ -26660,7 +27125,7 @@
     </row>
     <row r="25" spans="1:21">
       <c r="A25" s="30" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B25" s="31" t="s">
         <v>69</v>
@@ -26675,7 +27140,7 @@
         <v>60</v>
       </c>
       <c r="F25" s="31" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G25" s="31" t="s">
         <v>249</v>
@@ -26687,25 +27152,25 @@
         <v>4641652</v>
       </c>
       <c r="J25" s="31" t="s">
+        <v>368</v>
+      </c>
+      <c r="K25" s="31" t="s">
         <v>369</v>
-      </c>
-      <c r="K25" s="31" t="s">
-        <v>370</v>
       </c>
       <c r="L25" s="31" t="s">
         <v>67</v>
       </c>
       <c r="M25" s="31" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="N25" s="31" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="O25" s="64" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="P25" s="64" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="Q25" s="31">
         <v>640</v>
@@ -26714,17 +27179,17 @@
         <v>45</v>
       </c>
       <c r="S25" s="33" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="T25" s="9"/>
       <c r="U25" s="7"/>
     </row>
     <row r="26" spans="1:21">
       <c r="A26" s="43" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B26" s="44" t="s">
-        <v>312</v>
+        <v>705</v>
       </c>
       <c r="C26" s="44" t="s">
         <v>303</v>
@@ -26739,34 +27204,34 @@
         <v>563</v>
       </c>
       <c r="G26" s="44" t="s">
-        <v>265</v>
-      </c>
-      <c r="H26" s="44" t="s">
-        <v>185</v>
+        <v>704</v>
+      </c>
+      <c r="H26" s="67" t="s">
+        <v>703</v>
       </c>
       <c r="I26" s="45">
         <v>36717</v>
       </c>
       <c r="J26" s="44" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K26" s="45" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L26" s="45" t="s">
         <v>67</v>
       </c>
       <c r="M26" s="44" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="N26" s="44" t="s">
-        <v>314</v>
-      </c>
-      <c r="O26" s="67" t="s">
-        <v>634</v>
-      </c>
-      <c r="P26" s="67" t="s">
-        <v>669</v>
+        <v>313</v>
+      </c>
+      <c r="O26" s="66" t="s">
+        <v>633</v>
+      </c>
+      <c r="P26" s="66" t="s">
+        <v>668</v>
       </c>
       <c r="Q26" s="44">
         <v>504</v>
@@ -26782,52 +27247,52 @@
     </row>
     <row r="27" spans="1:21">
       <c r="A27" s="43" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B27" s="44" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C27" s="47" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D27" s="43" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="E27" s="44" t="s">
         <v>109</v>
       </c>
       <c r="F27" s="44" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="G27" s="44" t="s">
+        <v>445</v>
+      </c>
+      <c r="H27" s="44" t="s">
         <v>446</v>
-      </c>
-      <c r="H27" s="44" t="s">
-        <v>447</v>
       </c>
       <c r="I27" s="45">
         <v>27595</v>
       </c>
       <c r="J27" s="44" t="s">
+        <v>448</v>
+      </c>
+      <c r="K27" s="45" t="s">
         <v>449</v>
-      </c>
-      <c r="K27" s="45" t="s">
-        <v>450</v>
       </c>
       <c r="L27" s="44" t="s">
         <v>55</v>
       </c>
       <c r="M27" s="44" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="N27" s="44" t="s">
-        <v>452</v>
-      </c>
-      <c r="O27" s="67" t="s">
-        <v>635</v>
-      </c>
-      <c r="P27" s="67" t="s">
-        <v>670</v>
+        <v>451</v>
+      </c>
+      <c r="O27" s="66" t="s">
+        <v>634</v>
+      </c>
+      <c r="P27" s="66" t="s">
+        <v>669</v>
       </c>
       <c r="Q27" s="44">
         <v>264</v>
@@ -26836,14 +27301,14 @@
         <v>45</v>
       </c>
       <c r="S27" s="46" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="T27" s="9"/>
       <c r="U27" s="7"/>
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="43" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B28" s="44" t="s">
         <v>216</v>
@@ -26858,7 +27323,7 @@
         <v>109</v>
       </c>
       <c r="F28" s="44" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G28" s="44" t="s">
         <v>255</v>
@@ -26870,25 +27335,25 @@
         <v>160221</v>
       </c>
       <c r="J28" s="44" t="s">
+        <v>372</v>
+      </c>
+      <c r="K28" s="44" t="s">
+        <v>371</v>
+      </c>
+      <c r="L28" s="45" t="s">
+        <v>323</v>
+      </c>
+      <c r="M28" s="44" t="s">
+        <v>379</v>
+      </c>
+      <c r="N28" s="44" t="s">
         <v>373</v>
       </c>
-      <c r="K28" s="44" t="s">
-        <v>372</v>
-      </c>
-      <c r="L28" s="45" t="s">
-        <v>324</v>
-      </c>
-      <c r="M28" s="44" t="s">
-        <v>380</v>
-      </c>
-      <c r="N28" s="44" t="s">
-        <v>374</v>
-      </c>
-      <c r="O28" s="67" t="s">
-        <v>636</v>
-      </c>
-      <c r="P28" s="67" t="s">
-        <v>671</v>
+      <c r="O28" s="66" t="s">
+        <v>635</v>
+      </c>
+      <c r="P28" s="66" t="s">
+        <v>670</v>
       </c>
       <c r="Q28" s="44">
         <v>249</v>
@@ -26897,14 +27362,14 @@
         <v>45</v>
       </c>
       <c r="S28" s="46" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="T28" s="9"/>
       <c r="U28" s="7"/>
     </row>
     <row r="29" spans="1:21">
       <c r="A29" s="43" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B29" s="44" t="s">
         <v>51</v>
@@ -26919,7 +27384,7 @@
         <v>60</v>
       </c>
       <c r="F29" s="44" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G29" s="44" t="s">
         <v>245</v>
@@ -26931,7 +27396,7 @@
         <v>18227</v>
       </c>
       <c r="J29" s="44" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="K29" s="44" t="s">
         <v>50</v>
@@ -26940,16 +27405,16 @@
         <v>67</v>
       </c>
       <c r="M29" s="44" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="N29" s="45" t="s">
         <v>143</v>
       </c>
-      <c r="O29" s="67" t="s">
-        <v>637</v>
-      </c>
-      <c r="P29" s="67" t="s">
-        <v>672</v>
+      <c r="O29" s="66" t="s">
+        <v>636</v>
+      </c>
+      <c r="P29" s="66" t="s">
+        <v>671</v>
       </c>
       <c r="Q29" s="44">
         <v>653</v>
@@ -26965,7 +27430,7 @@
     </row>
     <row r="30" spans="1:21">
       <c r="A30" s="43" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B30" s="44" t="s">
         <v>49</v>
@@ -26980,7 +27445,7 @@
         <v>60</v>
       </c>
       <c r="F30" s="44" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G30" s="44" t="s">
         <v>244</v>
@@ -26992,25 +27457,25 @@
         <v>31754</v>
       </c>
       <c r="J30" s="44" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K30" s="44" t="s">
         <v>43</v>
       </c>
       <c r="L30" s="44" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="M30" s="44" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N30" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="O30" s="67" t="s">
-        <v>638</v>
-      </c>
-      <c r="P30" s="67" t="s">
-        <v>673</v>
+      <c r="O30" s="66" t="s">
+        <v>637</v>
+      </c>
+      <c r="P30" s="66" t="s">
+        <v>672</v>
       </c>
       <c r="Q30" s="44">
         <v>142</v>
@@ -27026,7 +27491,7 @@
     </row>
     <row r="31" spans="1:21">
       <c r="A31" s="43" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B31" s="44" t="s">
         <v>57</v>
@@ -27041,7 +27506,7 @@
         <v>60</v>
       </c>
       <c r="F31" s="44" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G31" s="44" t="s">
         <v>246</v>
@@ -27062,16 +27527,16 @@
         <v>63</v>
       </c>
       <c r="M31" s="44" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="N31" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="O31" s="67" t="s">
-        <v>639</v>
-      </c>
-      <c r="P31" s="67" t="s">
-        <v>674</v>
+      <c r="O31" s="66" t="s">
+        <v>638</v>
+      </c>
+      <c r="P31" s="66" t="s">
+        <v>673</v>
       </c>
       <c r="Q31" s="44">
         <v>191</v>
@@ -27080,14 +27545,14 @@
         <v>45</v>
       </c>
       <c r="S31" s="46" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="T31" s="9"/>
       <c r="U31" s="7"/>
     </row>
     <row r="32" spans="1:21">
       <c r="A32" s="43" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B32" s="44" t="s">
         <v>65</v>
@@ -27102,7 +27567,7 @@
         <v>60</v>
       </c>
       <c r="F32" s="44" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G32" s="44" t="s">
         <v>248</v>
@@ -27114,25 +27579,25 @@
         <v>38347</v>
       </c>
       <c r="J32" s="44" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="K32" s="44" t="s">
         <v>66</v>
       </c>
       <c r="L32" s="44" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="M32" s="44" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="N32" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="O32" s="67" t="s">
-        <v>640</v>
-      </c>
-      <c r="P32" s="67" t="s">
-        <v>675</v>
+      <c r="O32" s="66" t="s">
+        <v>639</v>
+      </c>
+      <c r="P32" s="66" t="s">
+        <v>674</v>
       </c>
       <c r="Q32" s="44">
         <v>174</v>
@@ -27141,14 +27606,14 @@
         <v>45</v>
       </c>
       <c r="S32" s="46" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="T32" s="9"/>
       <c r="U32" s="7"/>
     </row>
     <row r="33" spans="1:21">
       <c r="A33" s="43" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B33" s="44" t="s">
         <v>61</v>
@@ -27163,7 +27628,7 @@
         <v>60</v>
       </c>
       <c r="F33" s="44" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G33" s="44" t="s">
         <v>247</v>
@@ -27175,25 +27640,25 @@
         <v>44010</v>
       </c>
       <c r="J33" s="44" t="s">
+        <v>383</v>
+      </c>
+      <c r="K33" s="44" t="s">
         <v>384</v>
-      </c>
-      <c r="K33" s="44" t="s">
-        <v>385</v>
       </c>
       <c r="L33" s="44" t="s">
         <v>44</v>
       </c>
       <c r="M33" s="44" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="N33" s="45" t="s">
-        <v>386</v>
-      </c>
-      <c r="O33" s="67" t="s">
-        <v>386</v>
-      </c>
-      <c r="P33" s="67" t="s">
-        <v>676</v>
+        <v>385</v>
+      </c>
+      <c r="O33" s="66" t="s">
+        <v>385</v>
+      </c>
+      <c r="P33" s="66" t="s">
+        <v>675</v>
       </c>
       <c r="Q33" s="44">
         <v>1111</v>
@@ -27209,10 +27674,10 @@
     </row>
     <row r="34" spans="1:21">
       <c r="A34" s="43" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B34" s="44" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C34" s="44" t="s">
         <v>297</v>
@@ -27224,7 +27689,7 @@
         <v>60</v>
       </c>
       <c r="F34" s="44" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G34" s="44" t="s">
         <v>259</v>
@@ -27236,25 +27701,25 @@
         <v>48507</v>
       </c>
       <c r="J34" s="44" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K34" s="45" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L34" s="45" t="s">
         <v>67</v>
       </c>
       <c r="M34" s="44" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="N34" s="44" t="s">
-        <v>323</v>
-      </c>
-      <c r="O34" s="67" t="s">
-        <v>641</v>
-      </c>
-      <c r="P34" s="67" t="s">
-        <v>677</v>
+        <v>322</v>
+      </c>
+      <c r="O34" s="66" t="s">
+        <v>640</v>
+      </c>
+      <c r="P34" s="66" t="s">
+        <v>676</v>
       </c>
       <c r="Q34" s="44">
         <v>1132</v>
@@ -27270,52 +27735,52 @@
     </row>
     <row r="35" spans="1:21">
       <c r="A35" s="43" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B35" s="44" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C35" s="44" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D35" s="43" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="E35" s="44" t="s">
         <v>60</v>
       </c>
       <c r="F35" s="44" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="G35" s="44" t="s">
+        <v>441</v>
+      </c>
+      <c r="H35" s="44" t="s">
         <v>442</v>
-      </c>
-      <c r="H35" s="44" t="s">
-        <v>443</v>
       </c>
       <c r="I35" s="45">
         <v>43604</v>
       </c>
       <c r="J35" s="44" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="K35" s="45" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="L35" s="44" t="s">
         <v>67</v>
       </c>
       <c r="M35" s="44" t="s">
+        <v>443</v>
+      </c>
+      <c r="N35" s="44" t="s">
         <v>444</v>
       </c>
-      <c r="N35" s="44" t="s">
-        <v>445</v>
-      </c>
-      <c r="O35" s="67" t="s">
-        <v>642</v>
-      </c>
-      <c r="P35" s="67" t="s">
-        <v>678</v>
+      <c r="O35" s="66" t="s">
+        <v>641</v>
+      </c>
+      <c r="P35" s="66" t="s">
+        <v>677</v>
       </c>
       <c r="Q35" s="44">
         <v>648</v>
@@ -27324,20 +27789,20 @@
         <v>45</v>
       </c>
       <c r="S35" s="46" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="T35" s="9"/>
       <c r="U35" s="7"/>
     </row>
     <row r="36" spans="1:21">
       <c r="A36" s="43" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B36" s="44" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C36" s="44" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D36" s="43" t="s">
         <v>169</v>
@@ -27346,37 +27811,37 @@
         <v>60</v>
       </c>
       <c r="F36" s="44" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="G36" s="44" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H36" s="44" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="I36" s="45">
         <v>131326</v>
       </c>
       <c r="J36" s="44" t="s">
+        <v>458</v>
+      </c>
+      <c r="K36" s="45" t="s">
         <v>459</v>
-      </c>
-      <c r="K36" s="45" t="s">
-        <v>460</v>
       </c>
       <c r="L36" s="44" t="s">
         <v>67</v>
       </c>
       <c r="M36" s="44" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="N36" s="44" t="s">
-        <v>461</v>
-      </c>
-      <c r="O36" s="67" t="s">
-        <v>643</v>
-      </c>
-      <c r="P36" s="67" t="s">
-        <v>679</v>
+        <v>460</v>
+      </c>
+      <c r="O36" s="66" t="s">
+        <v>642</v>
+      </c>
+      <c r="P36" s="66" t="s">
+        <v>678</v>
       </c>
       <c r="Q36" s="44">
         <v>616</v>
@@ -27392,52 +27857,52 @@
     </row>
     <row r="37" spans="1:21">
       <c r="A37" s="43" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B37" s="44" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C37" s="44" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D37" s="48" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="E37" s="44" t="s">
         <v>60</v>
       </c>
       <c r="F37" s="45" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="G37" s="45" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H37" s="44" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="I37" s="45">
         <v>36892</v>
       </c>
       <c r="J37" s="44" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="K37" s="45" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="L37" s="44" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="M37" s="45" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="N37" s="44" t="s">
-        <v>464</v>
-      </c>
-      <c r="O37" s="67" t="s">
-        <v>644</v>
-      </c>
-      <c r="P37" s="67" t="s">
-        <v>680</v>
+        <v>463</v>
+      </c>
+      <c r="O37" s="66" t="s">
+        <v>643</v>
+      </c>
+      <c r="P37" s="66" t="s">
+        <v>679</v>
       </c>
       <c r="Q37" s="45">
         <v>393</v>
@@ -27468,7 +27933,7 @@
         <v>109</v>
       </c>
       <c r="F38" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G38" s="51" t="s">
         <v>258</v>
@@ -27480,13 +27945,13 @@
         <v>168903</v>
       </c>
       <c r="J38" s="51" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K38" s="51" t="s">
         <v>78</v>
       </c>
       <c r="L38" s="51" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M38" s="51" t="s">
         <v>102</v>
@@ -27498,7 +27963,7 @@
         <v>118</v>
       </c>
       <c r="P38" s="64" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="Q38" s="51">
         <v>1026</v>
@@ -27528,7 +27993,7 @@
         <v>109</v>
       </c>
       <c r="F39" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G39" s="51" t="s">
         <v>258</v>
@@ -27540,13 +28005,13 @@
         <v>168903</v>
       </c>
       <c r="J39" s="51" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K39" s="51" t="s">
         <v>84</v>
       </c>
       <c r="L39" s="51" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="M39" s="51" t="s">
         <v>106</v>
@@ -27558,7 +28023,7 @@
         <v>124</v>
       </c>
       <c r="P39" s="64" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="Q39" s="51">
         <v>527</v>
@@ -27588,7 +28053,7 @@
         <v>109</v>
       </c>
       <c r="F40" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G40" s="51" t="s">
         <v>265</v>
@@ -27600,7 +28065,7 @@
         <v>36717</v>
       </c>
       <c r="J40" s="51" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K40" s="51" t="s">
         <v>81</v>
@@ -27609,7 +28074,7 @@
         <v>67</v>
       </c>
       <c r="M40" s="51" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="N40" s="51" t="s">
         <v>121</v>
@@ -27618,7 +28083,7 @@
         <v>121</v>
       </c>
       <c r="P40" s="64" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="Q40" s="51">
         <v>328</v>
@@ -27648,7 +28113,7 @@
         <v>109</v>
       </c>
       <c r="F41" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G41" s="51" t="s">
         <v>260</v>
@@ -27660,13 +28125,13 @@
         <v>163826</v>
       </c>
       <c r="J41" s="51" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="K41" s="51" t="s">
         <v>88</v>
       </c>
       <c r="L41" s="51" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M41" s="51" t="s">
         <v>103</v>
@@ -27678,7 +28143,7 @@
         <v>128</v>
       </c>
       <c r="P41" s="64" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="Q41" s="51">
         <v>262</v>
@@ -27708,7 +28173,7 @@
         <v>109</v>
       </c>
       <c r="F42" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G42" s="51" t="s">
         <v>272</v>
@@ -27720,16 +28185,16 @@
         <v>66750</v>
       </c>
       <c r="J42" s="51" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="K42" s="51" t="s">
         <v>90</v>
       </c>
       <c r="L42" s="51" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="M42" s="51" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="N42" s="51" t="s">
         <v>131</v>
@@ -27738,7 +28203,7 @@
         <v>131</v>
       </c>
       <c r="P42" s="64" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="Q42" s="51">
         <v>247</v>
@@ -27768,7 +28233,7 @@
         <v>59</v>
       </c>
       <c r="F43" s="51" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G43" s="51" t="s">
         <v>250</v>
@@ -27780,16 +28245,16 @@
         <v>41724</v>
       </c>
       <c r="J43" s="51" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K43" s="51" t="s">
         <v>70</v>
       </c>
       <c r="L43" s="51" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="M43" s="51" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="N43" s="51" t="s">
         <v>110</v>
@@ -27798,7 +28263,7 @@
         <v>110</v>
       </c>
       <c r="P43" s="64" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="Q43" s="51">
         <v>667</v>
@@ -27807,7 +28272,7 @@
         <v>45</v>
       </c>
       <c r="S43" s="54" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="U43" s="7"/>
     </row>
@@ -27828,7 +28293,7 @@
         <v>59</v>
       </c>
       <c r="F44" s="51" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G44" s="51" t="s">
         <v>251</v>
@@ -27846,10 +28311,10 @@
         <v>71</v>
       </c>
       <c r="L44" s="51" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="M44" s="51" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="N44" s="51" t="s">
         <v>111</v>
@@ -27858,7 +28323,7 @@
         <v>111</v>
       </c>
       <c r="P44" s="64" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="Q44" s="51">
         <v>854</v>
@@ -27888,7 +28353,7 @@
         <v>59</v>
       </c>
       <c r="F45" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G45" s="51" t="s">
         <v>252</v>
@@ -27909,7 +28374,7 @@
         <v>44</v>
       </c>
       <c r="M45" s="51" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="N45" s="51" t="s">
         <v>112</v>
@@ -27918,7 +28383,7 @@
         <v>112</v>
       </c>
       <c r="P45" s="64" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="Q45" s="51">
         <v>811</v>
@@ -27939,7 +28404,7 @@
         <v>214</v>
       </c>
       <c r="C46" s="51" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D46" s="52" t="s">
         <v>4</v>
@@ -27948,7 +28413,7 @@
         <v>59</v>
       </c>
       <c r="F46" s="51" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G46" s="51" t="s">
         <v>253</v>
@@ -27978,7 +28443,7 @@
         <v>114</v>
       </c>
       <c r="P46" s="64" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="Q46" s="51">
         <v>623</v>
@@ -28008,7 +28473,7 @@
         <v>59</v>
       </c>
       <c r="F47" s="51" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G47" s="51" t="s">
         <v>254</v>
@@ -28020,7 +28485,7 @@
         <v>49797</v>
       </c>
       <c r="J47" s="51" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K47" s="51" t="s">
         <v>75</v>
@@ -28029,7 +28494,7 @@
         <v>44</v>
       </c>
       <c r="M47" s="51" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="N47" s="51" t="s">
         <v>115</v>
@@ -28038,7 +28503,7 @@
         <v>115</v>
       </c>
       <c r="P47" s="64" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="Q47" s="51">
         <v>883</v>
@@ -28068,7 +28533,7 @@
         <v>59</v>
       </c>
       <c r="F48" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G48" s="51" t="s">
         <v>256</v>
@@ -28098,7 +28563,7 @@
         <v>116</v>
       </c>
       <c r="P48" s="64" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="Q48" s="51">
         <v>632</v>
@@ -28116,7 +28581,7 @@
         <v>97</v>
       </c>
       <c r="B49" s="51" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C49" s="51" t="s">
         <v>295</v>
@@ -28128,7 +28593,7 @@
         <v>59</v>
       </c>
       <c r="F49" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G49" s="51" t="s">
         <v>257</v>
@@ -28140,7 +28605,7 @@
         <v>39937</v>
       </c>
       <c r="J49" s="51" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K49" s="51" t="s">
         <v>77</v>
@@ -28158,7 +28623,7 @@
         <v>117</v>
       </c>
       <c r="P49" s="64" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="Q49" s="51">
         <v>553</v>
@@ -28188,7 +28653,7 @@
         <v>59</v>
       </c>
       <c r="F50" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G50" s="51" t="s">
         <v>262</v>
@@ -28200,16 +28665,16 @@
         <v>815</v>
       </c>
       <c r="J50" s="51" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="K50" s="51" t="s">
         <v>80</v>
       </c>
       <c r="L50" s="51" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="M50" s="51" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="N50" s="51" t="s">
         <v>120</v>
@@ -28218,7 +28683,7 @@
         <v>120</v>
       </c>
       <c r="P50" s="64" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="Q50" s="51">
         <v>260</v>
@@ -28248,7 +28713,7 @@
         <v>59</v>
       </c>
       <c r="F51" s="51" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G51" s="51" t="s">
         <v>266</v>
@@ -28278,7 +28743,7 @@
         <v>122</v>
       </c>
       <c r="P51" s="64" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="Q51" s="51">
         <v>907</v>
@@ -28308,7 +28773,7 @@
         <v>59</v>
       </c>
       <c r="F52" s="51" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G52" s="51" t="s">
         <v>267</v>
@@ -28320,7 +28785,7 @@
         <v>49276</v>
       </c>
       <c r="J52" s="51" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K52" s="51" t="s">
         <v>83</v>
@@ -28338,7 +28803,7 @@
         <v>123</v>
       </c>
       <c r="P52" s="64" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="Q52" s="51">
         <v>907</v>
@@ -28368,7 +28833,7 @@
         <v>59</v>
       </c>
       <c r="F53" s="51" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="G53" s="51" t="s">
         <v>268</v>
@@ -28398,7 +28863,7 @@
         <v>132</v>
       </c>
       <c r="P53" s="64" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="Q53" s="51">
         <v>381</v>
@@ -28428,7 +28893,7 @@
         <v>59</v>
       </c>
       <c r="F54" s="51" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="G54" s="51" t="s">
         <v>269</v>
@@ -28440,16 +28905,16 @@
         <v>39672</v>
       </c>
       <c r="J54" s="51" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="K54" s="51" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L54" s="51" t="s">
         <v>44</v>
       </c>
       <c r="M54" s="51" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="N54" s="51" t="s">
         <v>125</v>
@@ -28458,7 +28923,7 @@
         <v>125</v>
       </c>
       <c r="P54" s="64" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="Q54" s="51">
         <v>1070</v>
@@ -28488,7 +28953,7 @@
         <v>59</v>
       </c>
       <c r="F55" s="51" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="G55" s="51" t="s">
         <v>270</v>
@@ -28500,13 +28965,13 @@
         <v>409</v>
       </c>
       <c r="J55" s="51" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K55" s="51" t="s">
         <v>86</v>
       </c>
       <c r="L55" s="51" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M55" s="51" t="s">
         <v>103</v>
@@ -28518,7 +28983,7 @@
         <v>126</v>
       </c>
       <c r="P55" s="64" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="Q55" s="51">
         <v>259</v>
@@ -28548,7 +29013,7 @@
         <v>60</v>
       </c>
       <c r="F56" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G56" s="51" t="s">
         <v>264</v>
@@ -28560,7 +29025,7 @@
         <v>1739</v>
       </c>
       <c r="J56" s="51" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K56" s="51" t="s">
         <v>87</v>
@@ -28578,7 +29043,7 @@
         <v>127</v>
       </c>
       <c r="P56" s="64" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="Q56" s="51">
         <v>216</v>
@@ -28608,7 +29073,7 @@
         <v>59</v>
       </c>
       <c r="F57" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G57" s="51" t="s">
         <v>263</v>
@@ -28620,13 +29085,13 @@
         <v>1714</v>
       </c>
       <c r="J57" s="51" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="K57" s="51" t="s">
         <v>89</v>
       </c>
       <c r="L57" s="51" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="M57" s="51" t="s">
         <v>103</v>
@@ -28638,7 +29103,7 @@
         <v>129</v>
       </c>
       <c r="P57" s="64" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="Q57" s="51">
         <v>262</v>
@@ -28668,7 +29133,7 @@
         <v>59</v>
       </c>
       <c r="F58" s="51" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="G58" s="51" t="s">
         <v>271</v>
@@ -28680,16 +29145,16 @@
         <v>38209</v>
       </c>
       <c r="J58" s="51" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="K58" s="51" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="L58" s="51" t="s">
         <v>67</v>
       </c>
       <c r="M58" s="51" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="N58" s="51" t="s">
         <v>130</v>
@@ -28698,7 +29163,7 @@
         <v>130</v>
       </c>
       <c r="P58" s="64" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="Q58" s="51">
         <v>557</v>
@@ -28728,7 +29193,7 @@
         <v>59</v>
       </c>
       <c r="F59" s="56" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="G59" s="56" t="s">
         <v>261</v>
@@ -28740,16 +29205,16 @@
         <v>19366</v>
       </c>
       <c r="J59" s="56" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="K59" s="51" t="s">
         <v>79</v>
       </c>
       <c r="L59" s="51" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="M59" s="56" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="N59" s="56" t="s">
         <v>119</v>
@@ -28758,7 +29223,7 @@
         <v>119</v>
       </c>
       <c r="P59" s="64" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="Q59" s="56">
         <v>854</v>
@@ -28926,7 +29391,7 @@
       <c r="A97"/>
       <c r="U97" s="7"/>
     </row>
-    <row r="98" spans="1:21" ht="15.75" thickBot="1">
+    <row r="98" spans="1:21" ht="15" thickBot="1">
       <c r="A98"/>
       <c r="U98" s="8"/>
     </row>
@@ -28950,22 +29415,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96255C4D-CE5F-4566-8D6C-2FA9A6F8A9CF}">
   <dimension ref="A1:C147"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" style="64" customWidth="1"/>
-    <col min="2" max="2" width="255.5703125" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" customWidth="1"/>
+    <col min="1" max="1" width="6.5546875" style="64" customWidth="1"/>
+    <col min="2" max="2" width="255.5546875" customWidth="1"/>
+    <col min="3" max="3" width="38.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="60" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="30">
+    <row r="2" spans="1:3">
       <c r="A2" s="61">
         <v>1</v>
       </c>
@@ -28989,7 +29454,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3" s="65" customFormat="1">
+    <row r="5" spans="1:3">
       <c r="A5" s="61">
         <v>4</v>
       </c>
@@ -29018,10 +29483,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="30">
+    <row r="9" spans="1:3" ht="28.8">
       <c r="A9" s="62">
         <v>8</v>
       </c>
@@ -29065,7 +29530,7 @@
     <row r="14" spans="1:3">
       <c r="A14" s="62"/>
       <c r="B14" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="C14" s="2"/>
     </row>
@@ -29083,7 +29548,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C16" s="2"/>
     </row>
@@ -29095,10 +29560,10 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="30">
+    <row r="18" spans="1:2" ht="28.8">
       <c r="A18" s="62"/>
       <c r="B18" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -29114,7 +29579,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -29122,13 +29587,13 @@
         <v>21</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="63"/>
       <c r="B22" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="16.5" customHeight="1">
@@ -29136,13 +29601,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="63"/>
       <c r="B24" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -29150,13 +29615,13 @@
         <v>23</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="63"/>
       <c r="B26" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -29164,13 +29629,13 @@
         <v>24</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="63"/>
       <c r="B28" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -29178,13 +29643,13 @@
         <v>25</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="63"/>
       <c r="B30" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -29192,13 +29657,13 @@
         <v>26</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="63"/>
       <c r="B32" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -29206,13 +29671,13 @@
         <v>27</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="63"/>
       <c r="B34" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -29220,7 +29685,7 @@
         <v>28</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -29228,7 +29693,7 @@
         <v>31</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -29236,7 +29701,7 @@
         <v>32</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -29244,7 +29709,7 @@
         <v>33</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -29252,13 +29717,13 @@
         <v>37</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="63"/>
-      <c r="B40" s="66" t="s">
-        <v>391</v>
+      <c r="B40" s="65" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -29266,13 +29731,13 @@
         <v>38</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="63"/>
       <c r="B42" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -29280,13 +29745,13 @@
         <v>39</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="63"/>
       <c r="B44" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -29294,19 +29759,19 @@
         <v>40</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="63"/>
       <c r="B46" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="63"/>
       <c r="B47" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="18" customHeight="1">
@@ -29314,13 +29779,13 @@
         <v>43</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="63"/>
       <c r="B49" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -29328,13 +29793,13 @@
         <v>44</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="63"/>
       <c r="B51" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -29342,7 +29807,7 @@
         <v>45</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -29350,13 +29815,13 @@
         <v>52</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="63"/>
       <c r="B54" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -29364,7 +29829,7 @@
         <v>53</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -29372,21 +29837,21 @@
         <v>54</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="63"/>
       <c r="B57" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="30">
+    <row r="58" spans="1:2" ht="28.8">
       <c r="A58" s="63">
         <v>55</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -29394,7 +29859,7 @@
         <v>56</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -29402,19 +29867,19 @@
         <v>62</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="63"/>
       <c r="B61" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="63"/>
       <c r="B62" s="6" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -29422,7 +29887,7 @@
         <v>65</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -29430,13 +29895,13 @@
         <v>66</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="63"/>
       <c r="B65" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -29444,7 +29909,7 @@
         <v>68</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -29452,7 +29917,7 @@
         <v>69</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -29460,7 +29925,7 @@
         <v>70</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -29468,7 +29933,7 @@
         <v>71</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -29476,7 +29941,7 @@
         <v>72</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -29484,7 +29949,7 @@
         <v>73</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -29492,7 +29957,7 @@
         <v>74</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -29500,7 +29965,7 @@
         <v>75</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -29508,7 +29973,7 @@
         <v>76</v>
       </c>
       <c r="B74" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -29516,7 +29981,7 @@
         <v>77</v>
       </c>
       <c r="B75" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -29524,7 +29989,7 @@
         <v>78</v>
       </c>
       <c r="B76" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -29532,7 +29997,7 @@
         <v>79</v>
       </c>
       <c r="B77" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -29540,7 +30005,7 @@
         <v>80</v>
       </c>
       <c r="B78" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -29548,7 +30013,7 @@
         <v>81</v>
       </c>
       <c r="B79" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -29556,7 +30021,7 @@
         <v>82</v>
       </c>
       <c r="B80" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -29564,7 +30029,7 @@
         <v>83</v>
       </c>
       <c r="B81" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -29572,7 +30037,7 @@
         <v>84</v>
       </c>
       <c r="B82" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="83" spans="1:2">
@@ -29580,7 +30045,7 @@
         <v>85</v>
       </c>
       <c r="B83" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="84" spans="1:2">
@@ -29588,12 +30053,12 @@
         <v>86</v>
       </c>
       <c r="B84" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
     </row>
     <row r="147" spans="3:3">
       <c r="C147" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -29736,13 +30201,34 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74D8BB12-B069-4D92-96D4-BAB5FBA637C8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74D8BB12-B069-4D92-96D4-BAB5FBA637C8}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD26D265-54B4-4B90-B51B-0FC70B0A7099}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD26D265-54B4-4B90-B51B-0FC70B0A7099}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2781A185-0111-49F6-AD42-5FB92A85FFC5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2781A185-0111-49F6-AD42-5FB92A85FFC5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>